--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,61 +628,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="B2" t="n">
-        <v>157.8</v>
+        <v>148.5</v>
       </c>
       <c r="C2" t="n">
-        <v>85.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="E2" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K2" t="n">
-        <v>98.7</v>
+        <v>98.2</v>
       </c>
       <c r="O2" t="n">
-        <v>40.5</v>
+        <v>39.8</v>
       </c>
       <c r="V2" t="n">
-        <v>4.6</v>
+        <v>11.2</v>
       </c>
       <c r="W2" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="X2" t="n">
-        <v>12.1</v>
+        <v>16.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>231.46</v>
+        <v>223.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.7</v>
+        <v>-3.83</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -691,10 +691,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>129.8</v>
+        <v>124.76</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.87</v>
+        <v>-3.64</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,66 +703,60 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46211</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="B3" t="n">
-        <v>151.6</v>
+        <v>147.5</v>
       </c>
       <c r="C3" t="n">
-        <v>73.8</v>
+        <v>72.8</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="n">
-        <v>33.9</v>
+        <v>31.4</v>
       </c>
       <c r="F3" t="n">
         <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>40.6</v>
+        <v>40.2</v>
       </c>
       <c r="V3" t="n">
-        <v>8.1</v>
+        <v>10.3</v>
       </c>
       <c r="W3" t="n">
-        <v>22.3</v>
+        <v>16.8</v>
       </c>
       <c r="X3" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3.1</v>
+        <v>0.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>229.92</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-1.54</v>
+        <v>4.8</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -771,10 +765,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.01</v>
+        <v>127.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.21</v>
+        <v>2.44</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -783,66 +777,93 @@
         <v>142</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46212</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B4" t="n">
-        <v>157.5</v>
+        <v>183.5</v>
       </c>
       <c r="C4" t="n">
-        <v>76.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D4" t="n">
-        <v>27.1</v>
+        <v>31.5</v>
       </c>
       <c r="E4" t="n">
-        <v>36.9</v>
+        <v>34.6</v>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.5</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" t="n">
+        <v>23</v>
       </c>
       <c r="V4" t="n">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="X4" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.1</v>
+        <v>6.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>226.95</v>
+        <v>220.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.97</v>
+        <v>-3.75</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -851,10 +872,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>128.4</v>
+        <v>127.13</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.61</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -862,67 +883,100 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL4" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46214</v>
+        <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>148.5</v>
+        <v>180.5</v>
       </c>
       <c r="C5" t="n">
-        <v>70.5</v>
+        <v>79.2</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8</v>
+        <v>30.7</v>
       </c>
       <c r="E5" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.9</v>
       </c>
       <c r="K5" t="n">
-        <v>98.2</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.7</v>
       </c>
       <c r="O5" t="n">
-        <v>39.8</v>
+        <v>42.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>23.1</v>
       </c>
       <c r="V5" t="n">
-        <v>11.2</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
       <c r="X5" t="n">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>223.11</v>
+        <v>219.64</v>
       </c>
       <c r="AG5" t="n">
-        <v>-3.83</v>
+        <v>-0.72</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -931,10 +985,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>124.76</v>
+        <v>126.03</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.64</v>
+        <v>-1.1</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -942,61 +996,100 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AP5" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>14.55</v>
+      </c>
       <c r="BL5" s="1" t="n">
-        <v>46214</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>147.5</v>
+        <v>168.1</v>
       </c>
       <c r="C6" t="n">
-        <v>72.8</v>
+        <v>69.7</v>
       </c>
       <c r="D6" t="n">
-        <v>26.7</v>
+        <v>30.4</v>
       </c>
       <c r="E6" t="n">
-        <v>31.4</v>
+        <v>33.9</v>
       </c>
       <c r="F6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.2</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>38.1</v>
       </c>
       <c r="O6" t="n">
-        <v>40.2</v>
+        <v>43.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>22.6</v>
       </c>
       <c r="V6" t="n">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="W6" t="n">
-        <v>16.8</v>
+        <v>22.9</v>
       </c>
       <c r="X6" t="n">
-        <v>13.6</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>14.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>224.93</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.29</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1005,10 +1098,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>127.2</v>
+        <v>129.28</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1016,94 +1109,100 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15.25</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B7" t="n">
-        <v>183.5</v>
+        <v>158.9</v>
       </c>
       <c r="C7" t="n">
-        <v>84.5</v>
+        <v>58.8</v>
       </c>
       <c r="D7" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="E7" t="n">
-        <v>34.6</v>
+        <v>30.4</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="H7" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="I7" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="J7" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>76.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="O7" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="W7" t="n">
+        <v>26</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z7" t="n">
         <v>20</v>
       </c>
-      <c r="X7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14</v>
-      </c>
       <c r="AA7" t="n">
-        <v>7.7</v>
+        <v>19.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>220.36</v>
+        <v>232.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.75</v>
+        <v>9.67</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1112,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>127.13</v>
+        <v>134.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>5.16</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1124,99 +1223,66 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>76.90000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.17</v>
+        <v>17.07</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B8" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>79.2</v>
+        <v>136.7</v>
       </c>
       <c r="D8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E8" t="n">
-        <v>34.6</v>
-      </c>
       <c r="F8" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41.9</v>
+        <v>7.5</v>
       </c>
       <c r="K8" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>37.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>23.1</v>
+        <v>39.2</v>
       </c>
       <c r="V8" t="n">
-        <v>9.1</v>
+        <v>17.1</v>
       </c>
       <c r="W8" t="n">
-        <v>20.8</v>
+        <v>36.1</v>
       </c>
       <c r="X8" t="n">
-        <v>14.9</v>
+        <v>26.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.9</v>
+        <v>20.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>219.64</v>
+        <v>235.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.72</v>
+        <v>3.09</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1225,10 +1291,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>126.03</v>
+        <v>137.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.1</v>
+        <v>3.06</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1236,100 +1302,61 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
-      <c r="AP8" t="n">
-        <v>82.95</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>14.55</v>
-      </c>
       <c r="BL8" s="1" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46218</v>
+        <v>46221</v>
       </c>
       <c r="B9" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>69.7</v>
+        <v>138.5</v>
       </c>
       <c r="D9" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33.9</v>
+        <v>31.7</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>41.2</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>38.1</v>
+        <v>91</v>
       </c>
       <c r="O9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22.6</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="n">
-        <v>11.2</v>
+        <v>13.2</v>
       </c>
       <c r="W9" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>224.93</v>
+        <v>231.99</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.29</v>
+        <v>-3.41</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1338,10 +1365,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>129.28</v>
+        <v>136.12</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.25</v>
+        <v>-1.38</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1349,100 +1376,94 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>15.25</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46218</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="B10" t="n">
-        <v>158.9</v>
+        <v>161.1</v>
       </c>
       <c r="C10" t="n">
-        <v>58.8</v>
+        <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>31.1</v>
+        <v>31.9</v>
       </c>
       <c r="E10" t="n">
-        <v>30.4</v>
+        <v>31.5</v>
       </c>
       <c r="F10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="I10" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="J10" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="K10" t="n">
-        <v>75.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="N10" t="n">
-        <v>37.8</v>
+        <v>35</v>
       </c>
       <c r="O10" t="n">
-        <v>41.4</v>
+        <v>37.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z10" t="n">
         <v>15</v>
       </c>
-      <c r="T10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>26</v>
-      </c>
-      <c r="X10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>20</v>
-      </c>
       <c r="AA10" t="n">
-        <v>19.3</v>
+        <v>11.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.5</v>
+        <v>-0.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>232.31</v>
+        <v>225.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.67</v>
+        <v>-6.48</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1451,10 +1472,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.44</v>
+        <v>133.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.16</v>
+        <v>-2.29</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1463,66 +1484,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>91.73999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>17.07</v>
+        <v>15.73</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46219</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B11" t="n">
-        <v>136.7</v>
+        <v>176.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>30.7</v>
+        <v>32.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.5</v>
       </c>
       <c r="K11" t="n">
-        <v>92.59999999999999</v>
+        <v>76</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36.4</v>
       </c>
       <c r="O11" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.3</v>
       </c>
       <c r="V11" t="n">
-        <v>17.1</v>
+        <v>11.5</v>
       </c>
       <c r="W11" t="n">
-        <v>36.1</v>
+        <v>15.5</v>
       </c>
       <c r="X11" t="n">
-        <v>26.6</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.5</v>
+        <v>11.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>-5.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.7</v>
+        <v>-1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>235.4</v>
+        <v>220.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.09</v>
+        <v>-4.59</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1531,10 +1585,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>137.5</v>
+        <v>131.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.06</v>
+        <v>-1.98</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1542,61 +1596,100 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15.49</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="B12" t="n">
-        <v>138.5</v>
+        <v>181</v>
+      </c>
+      <c r="C12" t="n">
+        <v>80.7</v>
       </c>
       <c r="D12" t="n">
-        <v>31.7</v>
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>35.1</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>5.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41.9</v>
       </c>
       <c r="K12" t="n">
-        <v>91</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.9</v>
       </c>
       <c r="O12" t="n">
-        <v>37.8</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="W12" t="n">
-        <v>22.5</v>
+        <v>13</v>
       </c>
       <c r="X12" t="n">
-        <v>17.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="n">
         <v>14</v>
       </c>
-      <c r="Z12" t="n">
-        <v>17</v>
-      </c>
       <c r="AA12" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>231.99</v>
+        <v>220.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>-3.41</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1605,10 +1698,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>136.12</v>
+        <v>130.06</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.38</v>
+        <v>-1.79</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1616,94 +1709,100 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14.93</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46221</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="B13" t="n">
-        <v>161.1</v>
+        <v>179.6</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>31.9</v>
+        <v>30.3</v>
       </c>
       <c r="E13" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="F13" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="I13" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J13" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K13" t="n">
-        <v>75.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>35</v>
+        <v>37.1</v>
       </c>
       <c r="O13" t="n">
-        <v>37.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>21.2</v>
       </c>
       <c r="T13" t="n">
-        <v>20.5</v>
+        <v>22.6</v>
       </c>
       <c r="V13" t="n">
-        <v>14.1</v>
+        <v>9.6</v>
       </c>
       <c r="W13" t="n">
-        <v>19.3</v>
+        <v>15.6</v>
       </c>
       <c r="X13" t="n">
-        <v>16.7</v>
+        <v>12.6</v>
       </c>
       <c r="Y13" t="n">
         <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
         <v>11.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>225.51</v>
+        <v>216.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>-6.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1712,10 +1811,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>133.83</v>
+        <v>127.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>-2.29</v>
+        <v>-2.21</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1724,99 +1823,99 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.93000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>15.73</v>
+        <v>15.16</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46222</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B14" t="n">
-        <v>176.4</v>
+        <v>170.4</v>
       </c>
       <c r="C14" t="n">
-        <v>77.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="D14" t="n">
-        <v>32.7</v>
+        <v>29.8</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>29.7</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="I14" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="J14" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="N14" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="O14" t="n">
-        <v>39.1</v>
+        <v>41.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>21.1</v>
       </c>
       <c r="T14" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
         <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>-5.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.3</v>
+        <v>4.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1825,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>131.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL14" t="n">
-        <v>-1.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1837,99 +1936,66 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>79.75</v>
+        <v>84.73</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.49</v>
+        <v>15.34</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B15" t="n">
-        <v>181</v>
-      </c>
-      <c r="C15" t="n">
-        <v>80.7</v>
+        <v>156</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" t="n">
-        <v>35.1</v>
+        <v>30.1</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41.9</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N15" t="n">
-        <v>36.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>22.5</v>
+        <v>39.2</v>
       </c>
       <c r="V15" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>13</v>
+        <v>20.9</v>
       </c>
       <c r="X15" t="n">
-        <v>11.8</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.4</v>
+        <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-6.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.9</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>220.92</v>
+        <v>224.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1938,10 +2004,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>130.06</v>
+        <v>130.92</v>
       </c>
       <c r="AL15" t="n">
-        <v>-1.79</v>
+        <v>2.38</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1949,100 +2015,61 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>79.94</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>14.93</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="B16" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>81.90000000000001</v>
+        <v>147.8</v>
       </c>
       <c r="D16" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
         <v>6.8</v>
       </c>
-      <c r="H16" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>42.3</v>
-      </c>
       <c r="K16" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>37.1</v>
+        <v>96.5</v>
       </c>
       <c r="O16" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>22.6</v>
+        <v>39.3</v>
       </c>
       <c r="V16" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>15.6</v>
+        <v>22.4</v>
       </c>
       <c r="X16" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-3.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>216.02</v>
+        <v>230.27</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>5.74</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2051,10 +2078,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>127.85</v>
+        <v>132.76</v>
       </c>
       <c r="AL16" t="n">
-        <v>-2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2062,100 +2089,94 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15.16</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="B17" t="n">
-        <v>170.4</v>
+        <v>149.1</v>
       </c>
       <c r="C17" t="n">
-        <v>78.5</v>
+        <v>60</v>
       </c>
       <c r="D17" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
-        <v>29.7</v>
+        <v>25.9</v>
       </c>
       <c r="F17" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="H17" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="J17" t="n">
-        <v>41.4</v>
+        <v>38.8</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="O17" t="n">
-        <v>41.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.3</v>
+        <v>21.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>21.1</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>23.3</v>
+        <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="W17" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="n">
         <v>15.7</v>
       </c>
-      <c r="X17" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>12.7</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.7</v>
+        <v>-0.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>216.02</v>
+        <v>237.43</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2164,10 +2185,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.54</v>
+        <v>134.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.19</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2176,66 +2197,66 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>84.73</v>
+        <v>91.28</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.34</v>
+        <v>16.95</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B18" t="n">
-        <v>156</v>
+        <v>143.9</v>
       </c>
       <c r="D18" t="n">
-        <v>30.1</v>
+        <v>32.9</v>
       </c>
       <c r="F18" t="n">
         <v>6.8</v>
       </c>
       <c r="K18" t="n">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="O18" t="n">
-        <v>39.2</v>
+        <v>37.9</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>20.9</v>
+        <v>25.6</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>17.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>224.53</v>
+        <v>236.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.32</v>
+        <v>-1.29</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2244,10 +2265,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>130.92</v>
+        <v>136.28</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2256,36 +2277,69 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="B19" t="n">
-        <v>147.8</v>
+        <v>166.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>63.7</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>34.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36.4</v>
       </c>
       <c r="F19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>39.9</v>
       </c>
       <c r="K19" t="n">
-        <v>96.5</v>
+        <v>75.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>35.9</v>
       </c>
       <c r="O19" t="n">
-        <v>39.3</v>
+        <v>39</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>20.3</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>11.9</v>
       </c>
       <c r="W19" t="n">
-        <v>22.4</v>
+        <v>27</v>
       </c>
       <c r="X19" t="n">
-        <v>15.2</v>
+        <v>19.4</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
@@ -2294,22 +2348,22 @@
         <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>230.27</v>
+        <v>236.13</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.74</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2318,10 +2372,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>132.76</v>
+        <v>134.54</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.84</v>
+        <v>-1.74</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2329,94 +2383,100 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AP19" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL19" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46229</v>
+        <v>46232</v>
       </c>
       <c r="B20" t="n">
-        <v>149.1</v>
+        <v>172.9</v>
       </c>
       <c r="C20" t="n">
-        <v>60</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>34.9</v>
       </c>
       <c r="E20" t="n">
-        <v>25.9</v>
+        <v>35.2</v>
       </c>
       <c r="F20" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="I20" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="J20" t="n">
-        <v>38.8</v>
+        <v>41.7</v>
       </c>
       <c r="K20" t="n">
-        <v>74.5</v>
+        <v>76.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="N20" t="n">
-        <v>36.7</v>
+        <v>34.8</v>
       </c>
       <c r="O20" t="n">
-        <v>40.1</v>
+        <v>37.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.7</v>
+        <v>19</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>21.7</v>
+        <v>19</v>
       </c>
       <c r="V20" t="n">
-        <v>10.3</v>
+        <v>14.4</v>
       </c>
       <c r="W20" t="n">
-        <v>24.4</v>
+        <v>18.7</v>
       </c>
       <c r="X20" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.7</v>
+        <v>12.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.4</v>
+        <v>-4.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>237.43</v>
+        <v>218.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>7.16</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2425,10 +2485,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.95</v>
+        <v>130.39</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.19</v>
+        <v>-4.15</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2437,66 +2497,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>91.28</v>
+        <v>78.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>16.95</v>
+        <v>15.79</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46229</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B21" t="n">
-        <v>143.9</v>
+        <v>157.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>68.5</v>
       </c>
       <c r="D21" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>27.7</v>
       </c>
       <c r="F21" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41.4</v>
       </c>
       <c r="K21" t="n">
-        <v>96.2</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34.9</v>
       </c>
       <c r="O21" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>15.1</v>
       </c>
       <c r="W21" t="n">
-        <v>25.6</v>
+        <v>23.1</v>
       </c>
       <c r="X21" t="n">
-        <v>17.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>16</v>
+        <v>13.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.4</v>
+        <v>-0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>236.14</v>
+        <v>218.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>-1.29</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2505,10 +2598,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>136.28</v>
+        <v>133.09</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2516,94 +2609,67 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>15.63</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B22" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="C22" t="n">
-        <v>63.7</v>
+        <v>137.6</v>
       </c>
       <c r="D22" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>36.4</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>39.9</v>
+        <v>6.5</v>
       </c>
       <c r="K22" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>35.9</v>
+        <v>96.7</v>
       </c>
       <c r="O22" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S22" t="n">
-        <v>6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>20.3</v>
+        <v>35.1</v>
       </c>
       <c r="V22" t="n">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="W22" t="n">
-        <v>27</v>
+        <v>24.4</v>
       </c>
       <c r="X22" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>14.4</v>
+        <v>17.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>-3.5</v>
+        <v>-0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.4</v>
+        <v>2.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>236.13</v>
+        <v>221.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.01</v>
+        <v>2.94</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2612,10 +2678,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>134.54</v>
+        <v>138.76</v>
       </c>
       <c r="AL22" t="n">
-        <v>-1.74</v>
+        <v>5.67</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2623,100 +2689,61 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
-      <c r="AP22" t="n">
-        <v>82.27</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>16.28</v>
-      </c>
       <c r="BL22" s="1" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46232</v>
+        <v>46235</v>
       </c>
       <c r="B23" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="C23" t="n">
-        <v>67.59999999999999</v>
+        <v>132.5</v>
       </c>
       <c r="D23" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E23" t="n">
-        <v>35.2</v>
+        <v>33.6</v>
       </c>
       <c r="F23" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I23" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>41.7</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>34.8</v>
+        <v>97.8</v>
       </c>
       <c r="O23" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q23" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
         <v>19</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>19</v>
-      </c>
-      <c r="V23" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>15</v>
-      </c>
       <c r="AA23" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-4.9</v>
+        <v>0.6</v>
       </c>
       <c r="AC23" t="n">
         <v>3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>218.6</v>
+        <v>224.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>-9.380000000000001</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2725,10 +2752,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>130.39</v>
+        <v>143.55</v>
       </c>
       <c r="AL23" t="n">
-        <v>-4.15</v>
+        <v>4.79</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2736,100 +2763,94 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
-      <c r="AP23" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15.79</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46232</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="B24" t="n">
-        <v>157.5</v>
+        <v>137.2</v>
       </c>
       <c r="C24" t="n">
-        <v>68.5</v>
+        <v>56.3</v>
       </c>
       <c r="D24" t="n">
-        <v>33.2</v>
+        <v>32.1</v>
       </c>
       <c r="E24" t="n">
-        <v>27.7</v>
+        <v>21.2</v>
       </c>
       <c r="F24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M24" t="n">
         <v>3.6</v>
       </c>
-      <c r="H24" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.6</v>
-      </c>
       <c r="N24" t="n">
-        <v>34.9</v>
+        <v>29</v>
       </c>
       <c r="O24" t="n">
-        <v>37.4</v>
+        <v>32.6</v>
       </c>
       <c r="Q24" t="n">
         <v>21.6</v>
       </c>
       <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
         <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>9</v>
       </c>
       <c r="T24" t="n">
         <v>21.6</v>
       </c>
       <c r="V24" t="n">
-        <v>15.1</v>
+        <v>10.7</v>
       </c>
       <c r="W24" t="n">
-        <v>23.1</v>
+        <v>24.3</v>
       </c>
       <c r="X24" t="n">
-        <v>19.1</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0</v>
+        <v>0.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>218.84</v>
+        <v>232.22</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.25</v>
+        <v>7.43</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2838,10 +2859,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>133.09</v>
+        <v>143.61</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.7</v>
+        <v>0.06</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2850,66 +2871,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>83.09999999999999</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.63</v>
+        <v>18.02</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B25" t="n">
-        <v>137.6</v>
+        <v>157.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>59.6</v>
       </c>
       <c r="D25" t="n">
         <v>35</v>
       </c>
+      <c r="E25" t="n">
+        <v>30.6</v>
+      </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>38.9</v>
       </c>
       <c r="K25" t="n">
-        <v>96.7</v>
+        <v>74.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>33.4</v>
       </c>
       <c r="O25" t="n">
-        <v>35.1</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="W25" t="n">
-        <v>24.4</v>
+        <v>26.3</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0</v>
+        <v>-2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>221.78</v>
+        <v>229.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.94</v>
+        <v>-2.53</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2918,10 +2972,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>138.76</v>
+        <v>136.96</v>
       </c>
       <c r="AL25" t="n">
-        <v>5.67</v>
+        <v>-6.65</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2929,61 +2983,100 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="B26" t="n">
-        <v>132.5</v>
+        <v>159.6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>63</v>
       </c>
       <c r="D26" t="n">
-        <v>33.6</v>
+        <v>34.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>31.1</v>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>40.5</v>
       </c>
       <c r="K26" t="n">
-        <v>97.8</v>
+        <v>75.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>34.3</v>
       </c>
       <c r="O26" t="n">
-        <v>31.6</v>
+        <v>38.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="W26" t="n">
-        <v>24.7</v>
+        <v>22.5</v>
       </c>
       <c r="X26" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6</v>
+        <v>-2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>224.78</v>
+        <v>228.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>-1.14</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2992,10 +3085,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>143.55</v>
+        <v>133.01</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.79</v>
+        <v>-3.95</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3003,94 +3096,100 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
+      <c r="AP26" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15.95</v>
+      </c>
       <c r="BL26" s="1" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
       <c r="B27" t="n">
-        <v>137.2</v>
+        <v>160.4</v>
       </c>
       <c r="C27" t="n">
-        <v>56.3</v>
+        <v>62.6</v>
       </c>
       <c r="D27" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2</v>
+        <v>32.2</v>
       </c>
       <c r="F27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H27" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="I27" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="J27" t="n">
-        <v>40.4</v>
+        <v>41.1</v>
       </c>
       <c r="K27" t="n">
         <v>75.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="N27" t="n">
-        <v>29</v>
+        <v>32.6</v>
       </c>
       <c r="O27" t="n">
-        <v>32.6</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T27" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="V27" t="n">
-        <v>10.7</v>
+        <v>16.4</v>
       </c>
       <c r="W27" t="n">
-        <v>24.3</v>
+        <v>22.8</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>232.22</v>
+        <v>225.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>7.43</v>
+        <v>-3.5</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3099,10 +3198,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>143.61</v>
+        <v>135.24</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.06</v>
+        <v>2.23</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3111,99 +3210,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>89.31999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>18.02</v>
+        <v>15.4</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B28" t="n">
-        <v>157.5</v>
+        <v>161.7</v>
       </c>
       <c r="C28" t="n">
-        <v>59.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E28" t="n">
-        <v>30.6</v>
+        <v>27.3</v>
       </c>
       <c r="F28" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="H28" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I28" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="J28" t="n">
-        <v>38.9</v>
+        <v>42.6</v>
       </c>
       <c r="K28" t="n">
-        <v>74.3</v>
+        <v>77</v>
       </c>
       <c r="M28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>21</v>
+      </c>
+      <c r="R28" t="n">
         <v>3.7</v>
       </c>
-      <c r="N28" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V28" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="W28" t="n">
-        <v>26.3</v>
+        <v>27</v>
       </c>
       <c r="X28" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>-2.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>-0.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>229.69</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="n">
-        <v>-2.53</v>
+        <v>-0.08</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3212,10 +3311,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>136.96</v>
+        <v>134.62</v>
       </c>
       <c r="AL28" t="n">
-        <v>-6.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3224,99 +3323,60 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>86.59</v>
+        <v>80.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>16.96</v>
+        <v>13.86</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B29" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="C29" t="n">
-        <v>63</v>
+        <v>151.5</v>
       </c>
       <c r="D29" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>31.1</v>
+        <v>35.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>21.3</v>
+        <v>5.4</v>
       </c>
       <c r="V29" t="n">
-        <v>17.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>22.5</v>
+        <v>19.4</v>
       </c>
       <c r="X29" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>228.57</v>
+        <v>221.37</v>
       </c>
       <c r="AG29" t="n">
-        <v>-1.14</v>
+        <v>0.05</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3325,10 +3385,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>133.01</v>
+        <v>135.21</v>
       </c>
       <c r="AL29" t="n">
-        <v>-3.95</v>
+        <v>0.59</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3336,100 +3396,61 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>15.95</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="B30" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C30" t="n">
-        <v>62.6</v>
+        <v>145.2</v>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
-      </c>
-      <c r="E30" t="n">
-        <v>32.2</v>
+        <v>33.5</v>
       </c>
       <c r="F30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I30" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>41.1</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N30" t="n">
-        <v>32.6</v>
+        <v>100.3</v>
       </c>
       <c r="O30" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>20.9</v>
+        <v>35.5</v>
       </c>
       <c r="V30" t="n">
-        <v>16.4</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
-        <v>22.8</v>
+        <v>19.2</v>
       </c>
       <c r="X30" t="n">
-        <v>19.6</v>
+        <v>13.1</v>
       </c>
       <c r="Y30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z30" t="n">
         <v>13</v>
       </c>
-      <c r="Z30" t="n">
-        <v>16</v>
-      </c>
       <c r="AA30" t="n">
-        <v>14.1</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.08</v>
+        <v>224.37</v>
       </c>
       <c r="AG30" t="n">
-        <v>-3.5</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3438,10 +3459,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.24</v>
+        <v>135.61</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.23</v>
+        <v>0.4</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3449,100 +3470,61 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
-      <c r="AP30" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>15.4</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B31" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C31" t="n">
-        <v>71.09999999999999</v>
+        <v>146.3</v>
       </c>
       <c r="D31" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>27.3</v>
+        <v>33.4</v>
       </c>
       <c r="F31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H31" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>42.6</v>
+        <v>5.5</v>
       </c>
       <c r="K31" t="n">
-        <v>77</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>31.5</v>
+        <v>98.2</v>
       </c>
       <c r="O31" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>21</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S31" t="n">
-        <v>6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>21</v>
+        <v>35.1</v>
       </c>
       <c r="V31" t="n">
-        <v>12.7</v>
+        <v>4.9</v>
       </c>
       <c r="W31" t="n">
-        <v>27</v>
+        <v>16.4</v>
       </c>
       <c r="X31" t="n">
-        <v>19.9</v>
+        <v>10.6</v>
       </c>
       <c r="Y31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA31" t="n">
         <v>9</v>
       </c>
-      <c r="Z31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB31" t="n">
-        <v>-5.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.3</v>
+        <v>-3.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>225</v>
+        <v>225.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.08</v>
+        <v>1.56</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3551,10 +3533,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>134.62</v>
+        <v>135.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.62</v>
+        <v>-0.33</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3562,61 +3544,94 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B32" t="n">
-        <v>151.5</v>
+        <v>182.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>86.8</v>
       </c>
       <c r="D32" t="n">
-        <v>35.1</v>
+        <v>31.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>33</v>
       </c>
       <c r="F32" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="n">
+        <v>22.4</v>
       </c>
       <c r="V32" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W32" t="n">
-        <v>19.4</v>
+        <v>15</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>-4.7</v>
+        <v>-10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>-1.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>221.37</v>
+        <v>218.63</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.05</v>
+        <v>-7.3</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3625,10 +3640,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>135.21</v>
+        <v>126.27</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.59</v>
+        <v>-9.01</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3636,61 +3651,100 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="B33" t="n">
-        <v>145.2</v>
+        <v>181.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>86.5</v>
       </c>
       <c r="D33" t="n">
-        <v>33.5</v>
+        <v>31.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>34.2</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>5.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41.9</v>
       </c>
       <c r="K33" t="n">
-        <v>100.3</v>
+        <v>76.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35.7</v>
       </c>
       <c r="O33" t="n">
-        <v>35.5</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>23</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>23</v>
       </c>
       <c r="V33" t="n">
         <v>7.1</v>
       </c>
       <c r="W33" t="n">
-        <v>19.2</v>
+        <v>14.8</v>
       </c>
       <c r="X33" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB33" t="n">
-        <v>-5.4</v>
+        <v>-4.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>224.37</v>
+        <v>216.39</v>
       </c>
       <c r="AG33" t="n">
-        <v>3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3699,10 +3753,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>135.61</v>
+        <v>123.32</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.4</v>
+        <v>-2.95</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3710,61 +3764,100 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>13.91</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46243</v>
+        <v>46246</v>
       </c>
       <c r="B34" t="n">
-        <v>146.3</v>
+        <v>183</v>
+      </c>
+      <c r="C34" t="n">
+        <v>84.7</v>
       </c>
       <c r="D34" t="n">
-        <v>33.4</v>
+        <v>30.9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>33.7</v>
       </c>
       <c r="F34" t="n">
-        <v>5.5</v>
+        <v>7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>42.3</v>
       </c>
       <c r="K34" t="n">
-        <v>98.2</v>
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>36.7</v>
       </c>
       <c r="O34" t="n">
-        <v>35.1</v>
+        <v>40.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23.6</v>
       </c>
       <c r="V34" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="W34" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="X34" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB34" t="n">
-        <v>-6.4</v>
+        <v>0.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>-3.3</v>
+        <v>1.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>225.93</v>
+        <v>217.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.56</v>
+        <v>0.76</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3773,10 +3866,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>135.28</v>
+        <v>117.87</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.33</v>
+        <v>-5.45</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3784,94 +3877,67 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>13.45</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46243</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B35" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="C35" t="n">
-        <v>86.8</v>
+        <v>163.8</v>
       </c>
       <c r="D35" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E35" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F35" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H35" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>41.1</v>
+        <v>6.5</v>
       </c>
       <c r="K35" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N35" t="n">
-        <v>33.5</v>
+        <v>101.2</v>
       </c>
       <c r="O35" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S35" t="n">
-        <v>15</v>
-      </c>
-      <c r="T35" t="n">
-        <v>22.4</v>
+        <v>40.2</v>
       </c>
       <c r="V35" t="n">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
       <c r="W35" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="X35" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
         <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AB35" t="n">
-        <v>-10.5</v>
+        <v>1.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>-5.1</v>
+        <v>2.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>218.63</v>
+        <v>220.31</v>
       </c>
       <c r="AG35" t="n">
-        <v>-7.3</v>
+        <v>3.16</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3880,10 +3946,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>126.27</v>
+        <v>116.52</v>
       </c>
       <c r="AL35" t="n">
-        <v>-9.01</v>
+        <v>-1.35</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3891,100 +3957,61 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>82.66</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>14.7</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B36" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="C36" t="n">
-        <v>86.5</v>
+        <v>155.9</v>
       </c>
       <c r="D36" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E36" t="n">
-        <v>34.2</v>
+        <v>28</v>
       </c>
       <c r="F36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>41.9</v>
+        <v>6.5</v>
       </c>
       <c r="K36" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>35.7</v>
+        <v>99.3</v>
       </c>
       <c r="O36" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>23</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S36" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>23</v>
+        <v>38.5</v>
       </c>
       <c r="V36" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="W36" t="n">
-        <v>14.8</v>
+        <v>15.8</v>
       </c>
       <c r="X36" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-4.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>-1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>216.39</v>
+        <v>221.99</v>
       </c>
       <c r="AG36" t="n">
-        <v>-2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3993,10 +4020,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>123.32</v>
+        <v>116.37</v>
       </c>
       <c r="AL36" t="n">
-        <v>-2.95</v>
+        <v>-0.15</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4004,100 +4031,61 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>13.91</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="B37" t="n">
-        <v>183</v>
-      </c>
-      <c r="C37" t="n">
-        <v>84.7</v>
+        <v>141.3</v>
       </c>
       <c r="D37" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E37" t="n">
-        <v>33.7</v>
+        <v>26.3</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>42.3</v>
+        <v>5.5</v>
       </c>
       <c r="K37" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4</v>
-      </c>
-      <c r="N37" t="n">
-        <v>36.7</v>
+        <v>97.8</v>
       </c>
       <c r="O37" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>23.6</v>
+        <v>39.8</v>
       </c>
       <c r="V37" t="n">
-        <v>5.7</v>
+        <v>9.5</v>
       </c>
       <c r="W37" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="X37" t="n">
-        <v>10.9</v>
+        <v>13.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>217.16</v>
+        <v>225.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.76</v>
+        <v>3.15</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4106,10 +4094,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>117.87</v>
+        <v>120.64</v>
       </c>
       <c r="AL37" t="n">
-        <v>-5.45</v>
+        <v>4.27</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4117,67 +4105,61 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
-      <c r="AP37" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL37" s="1" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B38" t="n">
-        <v>163.8</v>
+        <v>131.5</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>27.3</v>
       </c>
       <c r="F38" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K38" t="n">
-        <v>101.2</v>
+        <v>97</v>
       </c>
       <c r="O38" t="n">
-        <v>40.2</v>
+        <v>35.7</v>
       </c>
       <c r="V38" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="W38" t="n">
-        <v>17.2</v>
+        <v>13.9</v>
       </c>
       <c r="X38" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>-0.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>220.31</v>
+        <v>229.98</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.16</v>
+        <v>4.84</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4186,10 +4168,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>116.52</v>
+        <v>128.14</v>
       </c>
       <c r="AL38" t="n">
-        <v>-1.35</v>
+        <v>7.5</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4198,60 +4180,93 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B39" t="n">
-        <v>155.9</v>
+        <v>153</v>
+      </c>
+      <c r="C39" t="n">
+        <v>71.8</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>28.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>24.7</v>
       </c>
       <c r="F39" t="n">
-        <v>6.5</v>
+        <v>4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>41.1</v>
       </c>
       <c r="K39" t="n">
-        <v>99.3</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>33.5</v>
       </c>
       <c r="O39" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>23.2</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>11.2</v>
       </c>
       <c r="W39" t="n">
-        <v>15.8</v>
+        <v>13</v>
       </c>
       <c r="X39" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AF39" t="n">
-        <v>221.99</v>
+        <v>229.96</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.67</v>
+        <v>-0.02</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4260,10 +4275,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>116.37</v>
+        <v>128.15</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4271,61 +4286,100 @@
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="B40" t="n">
-        <v>141.3</v>
+        <v>165.8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>77.3</v>
       </c>
       <c r="D40" t="n">
-        <v>26.3</v>
+        <v>29.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>27.7</v>
       </c>
       <c r="F40" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>41.6</v>
       </c>
       <c r="K40" t="n">
-        <v>97.8</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N40" t="n">
+        <v>35.1</v>
       </c>
       <c r="O40" t="n">
         <v>39.8</v>
       </c>
+      <c r="Q40" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC40" t="n">
         <v>9.5</v>
       </c>
-      <c r="W40" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X40" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AD40" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>225.14</v>
+        <v>227.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.15</v>
+        <v>-2.95</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4333,61 +4387,112 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
+      <c r="AK40" t="n">
+        <v>128.86</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.71</v>
+      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
+      <c r="AP40" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>14.52</v>
+      </c>
       <c r="BL40" s="1" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="B41" t="n">
-        <v>131.5</v>
+        <v>158.1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>73.7</v>
       </c>
       <c r="D41" t="n">
-        <v>27.3</v>
+        <v>30.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26</v>
       </c>
       <c r="F41" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J41" t="n">
+        <v>40.9</v>
       </c>
       <c r="K41" t="n">
-        <v>97</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>35.3</v>
       </c>
       <c r="O41" t="n">
-        <v>35.7</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>23.6</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W41" t="n">
-        <v>13.9</v>
+        <v>19.3</v>
       </c>
       <c r="X41" t="n">
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AB41" t="n">
-        <v>-3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.4</v>
+        <v>6.5</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>228.35</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4395,100 +4500,112 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
+      <c r="AK41" t="n">
+        <v>130.88</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.02</v>
+      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>14.22</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46250</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B42" t="n">
-        <v>153</v>
+        <v>154.9</v>
       </c>
       <c r="C42" t="n">
-        <v>71.8</v>
+        <v>70.2</v>
       </c>
       <c r="D42" t="n">
-        <v>28.6</v>
+        <v>31.5</v>
       </c>
       <c r="E42" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="H42" t="n">
         <v>24.1</v>
       </c>
       <c r="I42" t="n">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="J42" t="n">
-        <v>41.1</v>
+        <v>40.3</v>
       </c>
       <c r="K42" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M42" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="N42" t="n">
-        <v>33.5</v>
+        <v>32.9</v>
       </c>
       <c r="O42" t="n">
-        <v>38.3</v>
+        <v>39</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="R42" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T42" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="V42" t="n">
-        <v>11.2</v>
+        <v>6.3</v>
       </c>
       <c r="W42" t="n">
-        <v>13</v>
+        <v>25.2</v>
       </c>
       <c r="X42" t="n">
-        <v>12.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="AB42" t="n">
-        <v>-6.6</v>
+        <v>2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.6</v>
+        <v>5.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>229.96</v>
+        <v>231.16</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.02</v>
+        <v>2.81</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4497,10 +4614,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>128.14</v>
+        <v>132.55</v>
       </c>
       <c r="AL42" t="n">
-        <v>11.77</v>
+        <v>1.67</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4509,99 +4626,66 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>87.47</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>14.8</v>
+        <v>13.1</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B43" t="n">
-        <v>165.8</v>
-      </c>
-      <c r="C43" t="n">
-        <v>77.3</v>
+        <v>152.2</v>
       </c>
       <c r="D43" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>41.6</v>
+        <v>3.5</v>
       </c>
       <c r="K43" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N43" t="n">
-        <v>35.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>7</v>
-      </c>
-      <c r="T43" t="n">
-        <v>23.8</v>
+        <v>34.4</v>
       </c>
       <c r="V43" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="W43" t="n">
-        <v>17.4</v>
+        <v>25.5</v>
       </c>
       <c r="X43" t="n">
-        <v>13.4</v>
+        <v>17.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA43" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>227.01</v>
+        <v>228.13</v>
       </c>
       <c r="AG43" t="n">
-        <v>-2.95</v>
+        <v>-3.03</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4610,10 +4694,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>128.15</v>
+        <v>128.02</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.01</v>
+        <v>-4.53</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4621,100 +4705,61 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>83.41</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>14.52</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="B44" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>73.7</v>
+        <v>143.9</v>
       </c>
       <c r="D44" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="F44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J44" t="n">
-        <v>40.9</v>
+        <v>2.5</v>
       </c>
       <c r="K44" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>35.3</v>
+        <v>99.2</v>
       </c>
       <c r="O44" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S44" t="n">
-        <v>7</v>
-      </c>
-      <c r="T44" t="n">
-        <v>23.6</v>
+        <v>35.2</v>
       </c>
       <c r="V44" t="n">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
       <c r="W44" t="n">
-        <v>19.3</v>
+        <v>17.6</v>
       </c>
       <c r="X44" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.4</v>
+        <v>-0.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD44" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AF44" t="n">
-        <v>228.35</v>
+        <v>229.16</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4723,10 +4768,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>128.86</v>
+        <v>127.06</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.71</v>
+        <v>-0.96</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4734,100 +4779,94 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
-      <c r="AP44" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>14.22</v>
-      </c>
       <c r="BL44" s="1" t="n">
-        <v>46253</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B45" t="n">
-        <v>154.9</v>
+        <v>163.2</v>
       </c>
       <c r="C45" t="n">
-        <v>70.2</v>
+        <v>73.7</v>
       </c>
       <c r="D45" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="F45" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="H45" t="n">
         <v>24.1</v>
       </c>
       <c r="I45" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="J45" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="K45" t="n">
-        <v>75.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="N45" t="n">
         <v>32.9</v>
       </c>
       <c r="O45" t="n">
-        <v>39</v>
+        <v>39.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="R45" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="S45" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V45" t="n">
-        <v>6.3</v>
+        <v>9.4</v>
       </c>
       <c r="W45" t="n">
-        <v>25.2</v>
+        <v>20.1</v>
       </c>
       <c r="X45" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA45" t="n">
-        <v>12.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.9</v>
+        <v>-0.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AF45" t="n">
-        <v>231.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.81</v>
+        <v>-0.61</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4836,10 +4875,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>130.88</v>
+        <v>125.61</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.02</v>
+        <v>-1.45</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4848,66 +4887,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>85.48999999999999</v>
+        <v>82.81</v>
       </c>
       <c r="AS45" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B46" t="n">
-        <v>152.2</v>
+        <v>174.4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>31</v>
+        <v>32.1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>30.8</v>
       </c>
       <c r="F46" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>24</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>39.5</v>
       </c>
       <c r="K46" t="n">
-        <v>98.40000000000001</v>
+        <v>74</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N46" t="n">
+        <v>35.8</v>
       </c>
       <c r="O46" t="n">
-        <v>34.4</v>
+        <v>42.6</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>23.1</v>
       </c>
       <c r="V46" t="n">
-        <v>9.5</v>
+        <v>12.8</v>
       </c>
       <c r="W46" t="n">
-        <v>25.5</v>
+        <v>22.1</v>
       </c>
       <c r="X46" t="n">
         <v>17.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA46" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AF46" t="n">
-        <v>228.13</v>
+        <v>219.99</v>
       </c>
       <c r="AG46" t="n">
-        <v>-3.03</v>
+        <v>-8.56</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4915,67 +4987,112 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
+      <c r="AK46" t="n">
+        <v>124.36</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>12.96</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B47" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>30.8</v>
+        <v>32.9</v>
+      </c>
+      <c r="E47" t="n">
+        <v>26</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
+      </c>
+      <c r="H47" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I47" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>40.1</v>
       </c>
       <c r="K47" t="n">
-        <v>99.2</v>
+        <v>71.3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>34.3</v>
       </c>
       <c r="O47" t="n">
-        <v>35.2</v>
+        <v>41.5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T47" t="n">
+        <v>23.1</v>
       </c>
       <c r="V47" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="W47" t="n">
-        <v>17.6</v>
+        <v>23.3</v>
       </c>
       <c r="X47" t="n">
-        <v>14.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z47" t="n">
         <v>14</v>
       </c>
       <c r="AA47" t="n">
-        <v>9</v>
+        <v>12.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>229.16</v>
+        <v>219.22</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.03</v>
+        <v>-0.77</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -4983,100 +5100,112 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
+      <c r="AK47" t="n">
+        <v>120.93</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>-3.43</v>
+      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
+      <c r="AP47" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>12.38</v>
+      </c>
       <c r="BL47" s="1" t="n">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B48" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C48" t="n">
-        <v>73.7</v>
+        <v>62.6</v>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="E48" t="n">
-        <v>28.2</v>
+        <v>24.6</v>
       </c>
       <c r="F48" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H48" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I48" t="n">
-        <v>11.4</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O48" t="n">
         <v>40.1</v>
       </c>
-      <c r="K48" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M48" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N48" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O48" t="n">
-        <v>39.7</v>
-      </c>
       <c r="Q48" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="R48" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="V48" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="W48" t="n">
-        <v>20.1</v>
+        <v>27.3</v>
       </c>
       <c r="X48" t="n">
-        <v>14.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z48" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>9.300000000000001</v>
+        <v>14</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>228.55</v>
+        <v>220.73</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.61</v>
+        <v>1.5</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5085,10 +5214,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>127.06</v>
+        <v>120.28</v>
       </c>
       <c r="AL48" t="n">
-        <v>-3.82</v>
+        <v>-0.65</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5097,99 +5226,99 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>82.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS48" t="n">
-        <v>12.9</v>
+        <v>13.26</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46257</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B49" t="n">
-        <v>174.4</v>
+        <v>150.7</v>
       </c>
       <c r="C49" t="n">
-        <v>75.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="D49" t="n">
-        <v>32.1</v>
+        <v>33.7</v>
       </c>
       <c r="E49" t="n">
-        <v>30.8</v>
+        <v>27.1</v>
       </c>
       <c r="F49" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I49" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="J49" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="K49" t="n">
-        <v>74</v>
+        <v>70.5</v>
       </c>
       <c r="M49" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="N49" t="n">
-        <v>35.8</v>
+        <v>33</v>
       </c>
       <c r="O49" t="n">
-        <v>42.6</v>
+        <v>38.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R49" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="S49" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V49" t="n">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="W49" t="n">
-        <v>22.1</v>
+        <v>28.9</v>
       </c>
       <c r="X49" t="n">
-        <v>17.5</v>
+        <v>21.7</v>
       </c>
       <c r="Y49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>219.99</v>
+        <v>220.58</v>
       </c>
       <c r="AG49" t="n">
-        <v>-8.56</v>
+        <v>-0.15</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5198,10 +5327,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>125.61</v>
+        <v>119.29</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.45</v>
+        <v>-0.99</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5210,99 +5339,60 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>77.83</v>
+        <v>77.22</v>
       </c>
       <c r="AS49" t="n">
-        <v>12.96</v>
+        <v>13.79</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B50" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="C50" t="n">
-        <v>70.90000000000001</v>
+        <v>138.2</v>
       </c>
       <c r="D50" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E50" t="n">
-        <v>26</v>
+        <v>33.6</v>
       </c>
       <c r="F50" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H50" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I50" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M50" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N50" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O50" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>5</v>
-      </c>
-      <c r="S50" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T50" t="n">
-        <v>23.1</v>
+        <v>6.1</v>
       </c>
       <c r="V50" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="W50" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="X50" t="n">
-        <v>16.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z50" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA50" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="AC50" t="n">
         <v>8.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>219.22</v>
+        <v>223.43</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.77</v>
+        <v>2.85</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5311,10 +5401,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>124.36</v>
+        <v>121.35</v>
       </c>
       <c r="AL50" t="n">
-        <v>-1.25</v>
+        <v>2.06</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5322,100 +5412,55 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>76.81</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>12.38</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B51" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="C51" t="n">
-        <v>62.6</v>
+        <v>126.5</v>
       </c>
       <c r="D51" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E51" t="n">
-        <v>24.6</v>
+        <v>33.2</v>
       </c>
       <c r="F51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H51" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I51" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K51" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M51" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4</v>
-      </c>
-      <c r="T51" t="n">
-        <v>23.2</v>
+        <v>3.4</v>
       </c>
       <c r="V51" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
       </c>
       <c r="W51" t="n">
-        <v>27.3</v>
+        <v>22.3</v>
       </c>
       <c r="X51" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z51" t="n">
         <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>9.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>220.73</v>
+        <v>229.48</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.5</v>
+        <v>6.05</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5424,10 +5469,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>120.93</v>
+        <v>128.37</v>
       </c>
       <c r="AL51" t="n">
-        <v>-3.43</v>
+        <v>7.02</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5435,100 +5480,94 @@
       <c r="AN51" t="n">
         <v>142</v>
       </c>
-      <c r="AP51" t="n">
-        <v>77.87</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>13.26</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46260</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B52" t="n">
-        <v>150.7</v>
+        <v>129.4</v>
       </c>
       <c r="C52" t="n">
-        <v>64.8</v>
+        <v>50.6</v>
       </c>
       <c r="D52" t="n">
-        <v>33.7</v>
+        <v>31.5</v>
       </c>
       <c r="E52" t="n">
-        <v>27.1</v>
+        <v>19.4</v>
       </c>
       <c r="F52" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="H52" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="I52" t="n">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="J52" t="n">
-        <v>39.9</v>
+        <v>38.9</v>
       </c>
       <c r="K52" t="n">
-        <v>70.5</v>
+        <v>73.3</v>
       </c>
       <c r="M52" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="N52" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="O52" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="Q52" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="R52" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="V52" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="W52" t="n">
-        <v>28.9</v>
+        <v>23.9</v>
       </c>
       <c r="X52" t="n">
-        <v>21.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="n">
-        <v>13.1</v>
+        <v>16.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="AF52" t="n">
-        <v>220.58</v>
+        <v>241.48</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.15</v>
+        <v>12</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5537,10 +5576,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>120.28</v>
+        <v>134.59</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.65</v>
+        <v>6.22</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5549,54 +5588,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>77.22</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AS52" t="n">
-        <v>13.79</v>
+        <v>15.97</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B53" t="n">
-        <v>138.2</v>
+        <v>142.9</v>
+      </c>
+      <c r="C53" t="n">
+        <v>52.7</v>
       </c>
       <c r="D53" t="n">
-        <v>33.6</v>
+        <v>34.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>24.8</v>
       </c>
       <c r="F53" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>22</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J53" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>70</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N53" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O53" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>19.7</v>
       </c>
       <c r="V53" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="W53" t="n">
-        <v>23.4</v>
+        <v>25.8</v>
       </c>
       <c r="X53" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="Y53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>238.69</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-2.8</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5604,61 +5688,112 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2.01</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>17.06</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="B54" t="n">
-        <v>126.5</v>
+        <v>148.1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>51.9</v>
       </c>
       <c r="D54" t="n">
-        <v>33.2</v>
+        <v>35.4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>31.5</v>
       </c>
       <c r="F54" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>71</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N54" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>20.7</v>
       </c>
       <c r="V54" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="W54" t="n">
-        <v>22.3</v>
+        <v>25.5</v>
       </c>
       <c r="X54" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC54" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>229.48</v>
+        <v>233.48</v>
       </c>
       <c r="AG54" t="n">
-        <v>6.05</v>
+        <v>-4.86</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5666,100 +5801,112 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
+      <c r="AK54" t="n">
+        <v>135.66</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
+      <c r="AP54" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>17.13</v>
+      </c>
       <c r="BL54" s="1" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="B55" t="n">
-        <v>129.4</v>
+        <v>143.4</v>
       </c>
       <c r="C55" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="D55" t="n">
-        <v>31.5</v>
+        <v>35.7</v>
       </c>
       <c r="E55" t="n">
-        <v>19.4</v>
+        <v>26.2</v>
       </c>
       <c r="F55" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I55" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K55" t="n">
-        <v>73.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
       <c r="O55" t="n">
-        <v>38</v>
+        <v>33.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="R55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="V55" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="W55" t="n">
-        <v>23.9</v>
+        <v>28.3</v>
       </c>
       <c r="X55" t="n">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z55" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="AC55" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AF55" t="n">
-        <v>229.5</v>
+        <v>235.13</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02</v>
+        <v>1.66</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5768,10 +5915,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.37</v>
+        <v>136.33</v>
       </c>
       <c r="AL55" t="n">
-        <v>8.09</v>
+        <v>0.67</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5780,75 +5927,66 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>91.59999999999999</v>
+        <v>88.27</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.97</v>
+        <v>17.6</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B56" t="n">
-        <v>142.9</v>
+        <v>144.9</v>
       </c>
       <c r="C56" t="n">
-        <v>52.7</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="E56" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="F56" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H56" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I56" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
-        <v>38.2</v>
+        <v>40.3</v>
       </c>
       <c r="K56" t="n">
-        <v>70</v>
+        <v>73.7</v>
       </c>
       <c r="M56" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="N56" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="O56" t="n">
-        <v>35.8</v>
+        <v>33.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="R56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V56" t="n">
-        <v>12</v>
-      </c>
-      <c r="W56" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>18.9</v>
+        <v>21</v>
       </c>
       <c r="Y56" t="n">
         <v>12</v>
@@ -5857,22 +5995,13 @@
         <v>19</v>
       </c>
       <c r="AA56" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.9</v>
+        <v>16.3</v>
       </c>
       <c r="AF56" t="n">
-        <v>238.69</v>
+        <v>234.87</v>
       </c>
       <c r="AG56" t="n">
-        <v>-2.8</v>
+        <v>-0.26</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5881,10 +6010,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>134.59</v>
+        <v>137.17</v>
       </c>
       <c r="AL56" t="n">
-        <v>6.22</v>
+        <v>0.84</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5893,81 +6022,42 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>89.05</v>
+        <v>87.09</v>
       </c>
       <c r="AS56" t="n">
-        <v>17.06</v>
+        <v>17.31</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B57" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>51.9</v>
+        <v>132.2</v>
       </c>
       <c r="D57" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="E57" t="n">
-        <v>31.5</v>
+        <v>35.6</v>
       </c>
       <c r="F57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H57" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J57" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K57" t="n">
-        <v>71</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N57" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="O57" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>20.7</v>
+        <v>4</v>
       </c>
       <c r="Y57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AF57" t="n">
-        <v>233.48</v>
+        <v>234.78</v>
       </c>
       <c r="AG57" t="n">
-        <v>-4.86</v>
+        <v>-0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5976,10 +6066,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>136.6</v>
+        <v>136.08</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.01</v>
+        <v>-1.09</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5987,82 +6077,37 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>17.13</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B58" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="C58" t="n">
-        <v>50.9</v>
+        <v>137.1</v>
       </c>
       <c r="D58" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E58" t="n">
-        <v>26.2</v>
+        <v>35.1</v>
       </c>
       <c r="F58" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J58" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="O58" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>21.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y58" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>17.9</v>
+        <v>10.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>235.13</v>
+        <v>229.75</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.66</v>
+        <v>-5.03</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6071,10 +6116,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>135.66</v>
+        <v>135.42</v>
       </c>
       <c r="AL58" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6082,82 +6127,76 @@
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>88.27</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>17.6</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="B59" t="n">
-        <v>144.9</v>
+        <v>166.2</v>
       </c>
       <c r="C59" t="n">
-        <v>53</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>35.6</v>
+        <v>32.7</v>
       </c>
       <c r="E59" t="n">
-        <v>26</v>
+        <v>28.1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H59" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="I59" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>40.3</v>
+        <v>42.1</v>
       </c>
       <c r="K59" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="M59" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="N59" t="n">
-        <v>31.6</v>
+        <v>33.7</v>
       </c>
       <c r="O59" t="n">
-        <v>33.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>23.7</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>21</v>
+        <v>23.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z59" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="n">
-        <v>16.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF59" t="n">
-        <v>234.87</v>
+        <v>222.86</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.26</v>
+        <v>-6.9</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6166,10 +6205,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>136.33</v>
+        <v>131.24</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.67</v>
+        <v>-4.18</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6178,42 +6217,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>87.09</v>
+        <v>81.98</v>
       </c>
       <c r="AS59" t="n">
-        <v>17.31</v>
+        <v>15.01</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B60" t="n">
-        <v>132.2</v>
+        <v>166.3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>74.90000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>35.6</v>
+        <v>32.8</v>
+      </c>
+      <c r="E60" t="n">
+        <v>28.8</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>4.2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N60" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z60" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF60" t="n">
-        <v>234.78</v>
+        <v>218.37</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.09</v>
+        <v>-4.49</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6221,43 +6299,55 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
+      <c r="AK60" t="n">
+        <v>129.21</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>-2.03</v>
+      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>12.97</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B61" t="n">
-        <v>137.1</v>
+        <v>135.8</v>
       </c>
       <c r="D61" t="n">
-        <v>35.1</v>
+        <v>34.6</v>
       </c>
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF61" t="n">
-        <v>229.75</v>
+        <v>220.85</v>
       </c>
       <c r="AG61" t="n">
-        <v>-5.03</v>
+        <v>2.48</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6272,36 +6362,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46270</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="B62" t="n">
-        <v>140.4</v>
+        <v>135.8</v>
       </c>
       <c r="D62" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z62" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>222.86</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>-6.9</v>
+        <v>14.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6316,7 +6400,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46271</v>
+        <v>46274</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -651,15 +651,6 @@
       <c r="O2" t="n">
         <v>39.8</v>
       </c>
-      <c r="V2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y2" t="n">
         <v>7</v>
       </c>
@@ -731,15 +722,6 @@
       <c r="O3" t="n">
         <v>40.2</v>
       </c>
-      <c r="V3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y3" t="n">
         <v>7</v>
       </c>
@@ -832,15 +814,6 @@
       <c r="T4" t="n">
         <v>23</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W4" t="n">
-        <v>20</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14.4</v>
-      </c>
       <c r="Y4" t="n">
         <v>4</v>
       </c>
@@ -945,15 +918,6 @@
       <c r="T5" t="n">
         <v>23.1</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>14.9</v>
-      </c>
       <c r="Y5" t="n">
         <v>8</v>
       </c>
@@ -1058,15 +1022,6 @@
       <c r="T6" t="n">
         <v>22.6</v>
       </c>
-      <c r="V6" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17</v>
-      </c>
       <c r="Y6" t="n">
         <v>11</v>
       </c>
@@ -1171,15 +1126,6 @@
       <c r="T7" t="n">
         <v>21.5</v>
       </c>
-      <c r="V7" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26</v>
-      </c>
-      <c r="X7" t="n">
-        <v>18.1</v>
-      </c>
       <c r="Y7" t="n">
         <v>17</v>
       </c>
@@ -1251,15 +1197,6 @@
       <c r="O8" t="n">
         <v>39.2</v>
       </c>
-      <c r="V8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>26.6</v>
-      </c>
       <c r="Y8" t="n">
         <v>18</v>
       </c>
@@ -1325,15 +1262,6 @@
       <c r="O9" t="n">
         <v>37.8</v>
       </c>
-      <c r="V9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>17.9</v>
-      </c>
       <c r="Y9" t="n">
         <v>14</v>
       </c>
@@ -1432,15 +1360,6 @@
       <c r="T10" t="n">
         <v>20.5</v>
       </c>
-      <c r="V10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
@@ -1545,15 +1464,6 @@
       <c r="T11" t="n">
         <v>22.3</v>
       </c>
-      <c r="V11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Y11" t="n">
         <v>9</v>
       </c>
@@ -1658,15 +1568,6 @@
       <c r="T12" t="n">
         <v>22.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>13</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y12" t="n">
         <v>10</v>
       </c>
@@ -1771,15 +1672,6 @@
       <c r="T13" t="n">
         <v>22.6</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y13" t="n">
         <v>9</v>
       </c>
@@ -1884,15 +1776,6 @@
       <c r="T14" t="n">
         <v>23.3</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X14" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y14" t="n">
         <v>8</v>
       </c>
@@ -1964,15 +1847,6 @@
       <c r="O15" t="n">
         <v>39.2</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X15" t="n">
-        <v>14</v>
-      </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
@@ -2038,15 +1912,6 @@
       <c r="O16" t="n">
         <v>39.3</v>
       </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y16" t="n">
         <v>11</v>
       </c>
@@ -2145,15 +2010,6 @@
       <c r="T17" t="n">
         <v>21.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W17" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y17" t="n">
         <v>12</v>
       </c>
@@ -2225,15 +2081,6 @@
       <c r="O18" t="n">
         <v>37.9</v>
       </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W18" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17.8</v>
-      </c>
       <c r="Y18" t="n">
         <v>13</v>
       </c>
@@ -2332,15 +2179,6 @@
       <c r="T19" t="n">
         <v>20.3</v>
       </c>
-      <c r="V19" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>27</v>
-      </c>
-      <c r="X19" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y19" t="n">
         <v>11</v>
       </c>
@@ -2445,15 +2283,6 @@
       <c r="T20" t="n">
         <v>19</v>
       </c>
-      <c r="V20" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X20" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y20" t="n">
         <v>9</v>
       </c>
@@ -2558,15 +2387,6 @@
       <c r="T21" t="n">
         <v>21.6</v>
       </c>
-      <c r="V21" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y21" t="n">
         <v>11</v>
       </c>
@@ -2638,15 +2458,6 @@
       <c r="O22" t="n">
         <v>35.1</v>
       </c>
-      <c r="V22" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>19</v>
-      </c>
       <c r="Y22" t="n">
         <v>14</v>
       </c>
@@ -2712,15 +2523,6 @@
       <c r="O23" t="n">
         <v>31.6</v>
       </c>
-      <c r="V23" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y23" t="n">
         <v>14</v>
       </c>
@@ -2819,15 +2621,6 @@
       <c r="T24" t="n">
         <v>21.6</v>
       </c>
-      <c r="V24" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y24" t="n">
         <v>12</v>
       </c>
@@ -2932,15 +2725,6 @@
       <c r="T25" t="n">
         <v>21.1</v>
       </c>
-      <c r="V25" t="n">
-        <v>13</v>
-      </c>
-      <c r="W25" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y25" t="n">
         <v>13</v>
       </c>
@@ -3045,15 +2829,6 @@
       <c r="T26" t="n">
         <v>21.3</v>
       </c>
-      <c r="V26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>20</v>
-      </c>
       <c r="Y26" t="n">
         <v>11</v>
       </c>
@@ -3158,15 +2933,6 @@
       <c r="T27" t="n">
         <v>20.9</v>
       </c>
-      <c r="V27" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X27" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y27" t="n">
         <v>13</v>
       </c>
@@ -3271,15 +3037,6 @@
       <c r="T28" t="n">
         <v>21</v>
       </c>
-      <c r="V28" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>27</v>
-      </c>
-      <c r="X28" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y28" t="n">
         <v>9</v>
       </c>
@@ -3345,15 +3102,6 @@
       <c r="F29" t="n">
         <v>5.4</v>
       </c>
-      <c r="V29" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W29" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X29" t="n">
-        <v>14</v>
-      </c>
       <c r="Y29" t="n">
         <v>5</v>
       </c>
@@ -3419,15 +3167,6 @@
       <c r="O30" t="n">
         <v>35.5</v>
       </c>
-      <c r="V30" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>13.1</v>
-      </c>
       <c r="Y30" t="n">
         <v>7</v>
       </c>
@@ -3493,15 +3232,6 @@
       <c r="O31" t="n">
         <v>35.1</v>
       </c>
-      <c r="V31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W31" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10.6</v>
-      </c>
       <c r="Y31" t="n">
         <v>3</v>
       </c>
@@ -3600,15 +3330,6 @@
       <c r="T32" t="n">
         <v>22.4</v>
       </c>
-      <c r="V32" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>15</v>
-      </c>
-      <c r="X32" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y32" t="n">
         <v>4</v>
       </c>
@@ -3713,15 +3434,6 @@
       <c r="T33" t="n">
         <v>23</v>
       </c>
-      <c r="V33" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X33" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y33" t="n">
         <v>6</v>
       </c>
@@ -3826,15 +3538,6 @@
       <c r="T34" t="n">
         <v>23.6</v>
       </c>
-      <c r="V34" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W34" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10.9</v>
-      </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
@@ -3906,15 +3609,6 @@
       <c r="O35" t="n">
         <v>40.2</v>
       </c>
-      <c r="V35" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W35" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y35" t="n">
         <v>8</v>
       </c>
@@ -3980,15 +3674,6 @@
       <c r="O36" t="n">
         <v>38.5</v>
       </c>
-      <c r="V36" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X36" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -4054,15 +3739,6 @@
       <c r="O37" t="n">
         <v>39.8</v>
       </c>
-      <c r="V37" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X37" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y37" t="n">
         <v>13</v>
       </c>
@@ -4128,15 +3804,6 @@
       <c r="O38" t="n">
         <v>35.7</v>
       </c>
-      <c r="V38" t="n">
-        <v>9</v>
-      </c>
-      <c r="W38" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X38" t="n">
-        <v>11.4</v>
-      </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
@@ -4235,15 +3902,6 @@
       <c r="T39" t="n">
         <v>23.2</v>
       </c>
-      <c r="V39" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W39" t="n">
-        <v>13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y39" t="n">
         <v>12</v>
       </c>
@@ -4348,15 +4006,6 @@
       <c r="T40" t="n">
         <v>23.8</v>
       </c>
-      <c r="V40" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W40" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X40" t="n">
-        <v>13.4</v>
-      </c>
       <c r="Y40" t="n">
         <v>7</v>
       </c>
@@ -4461,15 +4110,6 @@
       <c r="T41" t="n">
         <v>23.6</v>
       </c>
-      <c r="V41" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W41" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X41" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y41" t="n">
         <v>6</v>
       </c>
@@ -4574,15 +4214,6 @@
       <c r="T42" t="n">
         <v>23.7</v>
       </c>
-      <c r="V42" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W42" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X42" t="n">
-        <v>15.8</v>
-      </c>
       <c r="Y42" t="n">
         <v>8</v>
       </c>
@@ -4654,15 +4285,6 @@
       <c r="O43" t="n">
         <v>34.4</v>
       </c>
-      <c r="V43" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X43" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y43" t="n">
         <v>6</v>
       </c>
@@ -4728,15 +4350,6 @@
       <c r="O44" t="n">
         <v>35.2</v>
       </c>
-      <c r="V44" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W44" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X44" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y44" t="n">
         <v>4</v>
       </c>
@@ -4835,15 +4448,6 @@
       <c r="T45" t="n">
         <v>23.5</v>
       </c>
-      <c r="V45" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W45" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>14.8</v>
-      </c>
       <c r="Y45" t="n">
         <v>4</v>
       </c>
@@ -4948,15 +4552,6 @@
       <c r="T46" t="n">
         <v>23.1</v>
       </c>
-      <c r="V46" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W46" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y46" t="n">
         <v>7</v>
       </c>
@@ -5061,15 +4656,6 @@
       <c r="T47" t="n">
         <v>23.1</v>
       </c>
-      <c r="V47" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y47" t="n">
         <v>8</v>
       </c>
@@ -5174,15 +4760,6 @@
       <c r="T48" t="n">
         <v>23.2</v>
       </c>
-      <c r="V48" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y48" t="n">
         <v>10</v>
       </c>
@@ -5287,15 +4864,6 @@
       <c r="T49" t="n">
         <v>23.2</v>
       </c>
-      <c r="V49" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="X49" t="n">
-        <v>21.7</v>
-      </c>
       <c r="Y49" t="n">
         <v>10</v>
       </c>
@@ -5361,15 +4929,6 @@
       <c r="F50" t="n">
         <v>6.1</v>
       </c>
-      <c r="V50" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y50" t="n">
         <v>9</v>
       </c>
@@ -5429,15 +4988,6 @@
       <c r="F51" t="n">
         <v>3.4</v>
       </c>
-      <c r="V51" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y51" t="n">
         <v>8</v>
       </c>
@@ -5536,15 +5086,6 @@
       <c r="T52" t="n">
         <v>21.4</v>
       </c>
-      <c r="V52" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W52" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X52" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y52" t="n">
         <v>8</v>
       </c>
@@ -5649,15 +5190,6 @@
       <c r="T53" t="n">
         <v>19.7</v>
       </c>
-      <c r="V53" t="n">
-        <v>12</v>
-      </c>
-      <c r="W53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X53" t="n">
-        <v>18.9</v>
-      </c>
       <c r="Y53" t="n">
         <v>12</v>
       </c>
@@ -5762,15 +5294,6 @@
       <c r="T54" t="n">
         <v>20.7</v>
       </c>
-      <c r="V54" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X54" t="n">
-        <v>19.3</v>
-      </c>
       <c r="Y54" t="n">
         <v>10</v>
       </c>
@@ -5875,15 +5398,6 @@
       <c r="T55" t="n">
         <v>21.6</v>
       </c>
-      <c r="V55" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W55" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>20.6</v>
-      </c>
       <c r="Y55" t="n">
         <v>11</v>
       </c>
@@ -5997,6 +5511,15 @@
       <c r="AA56" t="n">
         <v>16.3</v>
       </c>
+      <c r="AB56" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF56" t="n">
         <v>234.87</v>
       </c>
@@ -6354,6 +5877,12 @@
       </c>
       <c r="AI61" t="n">
         <v>235</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>129.07</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>-0.14</v>
       </c>
       <c r="AM61" t="n">
         <v>110</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,52 +628,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B2" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C2" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F2" t="n">
         <v>7.4</v>
       </c>
       <c r="K2" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y2" t="n">
         <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -682,10 +685,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -694,51 +697,93 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B3" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C3" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D3" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E3" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41.5</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>23</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>20</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -747,10 +792,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -758,85 +803,100 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
+      <c r="AP3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B4" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C4" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E4" t="n">
         <v>34.6</v>
       </c>
       <c r="F4" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H4" t="n">
         <v>23.9</v>
       </c>
       <c r="I4" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J4" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K4" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T4" t="n">
-        <v>23</v>
+        <v>23.1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -845,10 +905,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -857,90 +917,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C5" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D5" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E5" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J5" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O5" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
         <v>17.6</v>
       </c>
       <c r="T5" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.9</v>
+        <v>14.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -949,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -961,90 +1030,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B6" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C6" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D6" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E6" t="n">
         <v>30.4</v>
       </c>
-      <c r="E6" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I6" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O6" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T6" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>18.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1053,10 +1131,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1065,90 +1143,66 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B7" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D7" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K7" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>26.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC7" t="n">
         <v>6.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1157,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1168,58 +1222,61 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
-      <c r="AP7" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B8" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D8" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1228,10 +1285,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1240,51 +1297,93 @@
         <v>142</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B9" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.1</v>
       </c>
       <c r="K9" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>35</v>
       </c>
       <c r="O9" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1293,10 +1392,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1304,85 +1403,100 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B10" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E10" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I10" t="n">
         <v>11.4</v>
       </c>
       <c r="J10" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K10" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O10" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T10" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1391,10 +1505,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL10" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1403,90 +1517,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B11" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C11" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D11" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA11" t="n">
         <v>11.4</v>
       </c>
-      <c r="J11" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>76</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>14</v>
-      </c>
-      <c r="T11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB11" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF11" t="n">
         <v>220.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1495,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1507,90 +1630,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B12" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C12" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E12" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I12" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J12" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K12" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O12" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD12" t="n">
         <v>0.5</v>
       </c>
-      <c r="S12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF12" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1599,10 +1731,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1611,90 +1743,99 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B13" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C13" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D13" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E13" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I13" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J13" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K13" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O13" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T13" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
         <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF13" t="n">
         <v>216.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1703,10 +1844,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL13" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1715,90 +1856,66 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS13" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B14" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D14" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F14" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K14" t="n">
-        <v>75</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X14" t="n">
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1807,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1818,58 +1935,61 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B15" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D15" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
         <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O15" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>15.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
         <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1878,10 +1998,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1890,51 +2010,93 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B16" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25.9</v>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>24</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38.8</v>
       </c>
       <c r="K16" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>36.7</v>
       </c>
       <c r="O16" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG16" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -1943,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -1954,85 +2116,67 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B17" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
-      </c>
-      <c r="E17" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>24</v>
-      </c>
-      <c r="I17" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K17" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O17" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2041,10 +2185,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2052,58 +2196,94 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B18" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>63.7</v>
       </c>
       <c r="D18" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>36.4</v>
       </c>
       <c r="F18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>39.9</v>
       </c>
       <c r="K18" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>35.9</v>
       </c>
       <c r="O18" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>27</v>
+      </c>
+      <c r="X18" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2112,10 +2292,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2123,85 +2303,100 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B19" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C19" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E19" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H19" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I19" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K19" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N19" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O19" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>20.3</v>
+        <v>19</v>
+      </c>
+      <c r="V19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2210,10 +2405,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2222,90 +2417,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B20" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C20" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D20" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E20" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F20" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H20" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I20" t="n">
         <v>11.3</v>
       </c>
       <c r="J20" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K20" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N20" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O20" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>19</v>
+        <v>21.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2314,10 +2518,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL20" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2326,90 +2530,66 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B21" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D21" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I21" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K21" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O21" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB21" t="n">
         <v>-0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2418,10 +2598,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2429,58 +2609,61 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B22" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F22" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O22" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
+      </c>
+      <c r="V22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y22" t="n">
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2489,10 +2672,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2501,51 +2684,93 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B23" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>56.3</v>
       </c>
       <c r="D23" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21.2</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>40.4</v>
       </c>
       <c r="K23" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>29</v>
       </c>
       <c r="O23" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2554,10 +2779,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2565,52 +2790,58 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B24" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C24" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D24" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H24" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J24" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K24" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O24" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
@@ -2619,31 +2850,40 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG24" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2652,10 +2892,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2664,90 +2904,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS24" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B25" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C25" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F25" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H25" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I25" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J25" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K25" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O25" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>20</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2756,10 +3005,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL25" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2768,90 +3017,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B26" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C26" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D26" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F26" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I26" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J26" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K26" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N26" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O26" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
+      </c>
+      <c r="V26" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X26" t="n">
+        <v>19.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2860,10 +3118,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL26" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2872,90 +3130,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B27" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C27" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E27" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H27" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I27" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J27" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K27" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M27" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N27" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O27" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>20.9</v>
+        <v>21</v>
+      </c>
+      <c r="V27" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>27</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -2964,10 +3231,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -2976,90 +3243,60 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B28" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C28" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D28" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>77</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N28" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>21</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>21</v>
+        <v>5.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W28" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA28" t="n">
         <v>9</v>
       </c>
-      <c r="Z28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB28" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3068,10 +3305,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3079,52 +3316,61 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B29" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D29" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F29" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
         <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB29" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3133,10 +3379,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3145,51 +3391,60 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B30" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D30" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O30" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB30" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3198,10 +3453,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3210,51 +3465,93 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B31" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>86.8</v>
       </c>
       <c r="D31" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>41.1</v>
       </c>
       <c r="K31" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>33.5</v>
       </c>
       <c r="O31" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3263,10 +3560,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3274,85 +3571,100 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B32" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C32" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D32" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H32" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I32" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J32" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K32" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M32" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O32" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T32" t="n">
-        <v>22.4</v>
+        <v>23</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
         <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG32" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3361,10 +3673,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3373,90 +3685,99 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS32" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B33" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C33" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D33" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E33" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F33" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I33" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J33" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K33" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O33" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R33" t="n">
         <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T33" t="n">
-        <v>23</v>
+        <v>23.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>10.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB33" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD33" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF33" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3465,10 +3786,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL33" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3477,90 +3798,66 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B34" t="n">
-        <v>183</v>
-      </c>
-      <c r="C34" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D34" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E34" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K34" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O34" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S34" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T34" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
         <v>10</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3569,10 +3866,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL34" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3580,58 +3877,61 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B35" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F35" t="n">
         <v>6.5</v>
       </c>
       <c r="K35" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O35" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>12.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3640,10 +3940,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3652,51 +3952,60 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B36" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F36" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K36" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O36" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X36" t="n">
+        <v>13.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3705,10 +4014,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>116.37</v>
+        <v>120.64</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.15</v>
+        <v>4.27</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3717,51 +4026,60 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B37" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D37" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F37" t="n">
         <v>5.5</v>
       </c>
       <c r="K37" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O37" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X37" t="n">
+        <v>11.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA37" t="n">
         <v>15</v>
       </c>
-      <c r="AA37" t="n">
-        <v>14</v>
-      </c>
       <c r="AB37" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>225.14</v>
+        <v>229.98</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.15</v>
+        <v>4.84</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -3770,10 +4088,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>120.64</v>
+        <v>128.14</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.27</v>
+        <v>7.5</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -3782,51 +4100,93 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B38" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C38" t="n">
+        <v>71.8</v>
       </c>
       <c r="D38" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>24.7</v>
       </c>
       <c r="F38" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>41.1</v>
       </c>
       <c r="K38" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>33.5</v>
       </c>
       <c r="O38" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>13</v>
+      </c>
+      <c r="X38" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.98</v>
+        <v>229.96</v>
       </c>
       <c r="AG38" t="n">
-        <v>4.84</v>
+        <v>-0.02</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -3835,10 +4195,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL38" t="n">
-        <v>7.5</v>
+        <v>0.01</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -3846,85 +4206,100 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B39" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C39" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D39" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E39" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H39" t="n">
         <v>24.1</v>
       </c>
       <c r="I39" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J39" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K39" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N39" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O39" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
+      </c>
+      <c r="V39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W39" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF39" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -3933,10 +4308,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -3945,90 +4320,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS39" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B40" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C40" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D40" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E40" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H40" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K40" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O40" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R40" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X40" t="n">
+        <v>14.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG40" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4037,10 +4421,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4049,90 +4433,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS40" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B41" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C41" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D41" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F41" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H41" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I41" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J41" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K41" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N41" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O41" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R41" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T41" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>15.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4141,10 +4534,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>130.88</v>
+        <v>132.55</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4153,90 +4546,66 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B42" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C42" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D42" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H42" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J42" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T42" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC42" t="n">
         <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4245,10 +4614,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>132.55</v>
+        <v>128.02</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.67</v>
+        <v>-4.53</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4256,58 +4625,61 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B43" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D43" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F43" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K43" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O43" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
+      </c>
+      <c r="V43" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W43" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X43" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA43" t="n">
         <v>9</v>
       </c>
       <c r="AB43" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF43" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG43" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4316,10 +4688,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>128.02</v>
+        <v>127.06</v>
       </c>
       <c r="AL43" t="n">
-        <v>-4.53</v>
+        <v>-0.96</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4328,51 +4700,93 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B44" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>73.7</v>
       </c>
       <c r="D44" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E44" t="n">
+        <v>28.2</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>40.1</v>
       </c>
       <c r="K44" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N44" t="n">
+        <v>32.9</v>
       </c>
       <c r="O44" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>14.8</v>
       </c>
       <c r="Y44" t="n">
         <v>4</v>
       </c>
       <c r="Z44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA44" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4381,10 +4795,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.96</v>
+        <v>-1.45</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4392,85 +4806,100 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B45" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C45" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E45" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F45" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H45" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J45" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K45" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M45" t="n">
         <v>6.8</v>
       </c>
       <c r="N45" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O45" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T45" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>17.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z45" t="n">
         <v>13</v>
       </c>
       <c r="AA45" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC45" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB45" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD45" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4479,10 +4908,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4491,90 +4920,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B46" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C46" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E46" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F46" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H46" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I46" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J46" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K46" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M46" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N46" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O46" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q46" t="n">
         <v>23.1</v>
       </c>
       <c r="R46" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T46" t="n">
         <v>23.1</v>
       </c>
+      <c r="V46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA46" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG46" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4583,10 +5021,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL46" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4595,90 +5033,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS46" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B47" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C47" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D47" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E47" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F47" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H47" t="n">
         <v>23.8</v>
       </c>
       <c r="I47" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J47" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K47" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O47" t="n">
         <v>40.1</v>
       </c>
-      <c r="K47" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O47" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q47" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S47" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z47" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA47" t="n">
         <v>14</v>
       </c>
-      <c r="AA47" t="n">
-        <v>12.2</v>
-      </c>
       <c r="AB47" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -4687,10 +5134,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL47" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -4699,67 +5146,76 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS47" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B48" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C48" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D48" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E48" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F48" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H48" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I48" t="n">
         <v>7.2</v>
       </c>
       <c r="J48" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K48" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M48" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N48" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O48" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q48" t="n">
         <v>23.2</v>
       </c>
       <c r="R48" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
         <v>23.2</v>
       </c>
+      <c r="V48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X48" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y48" t="n">
         <v>10</v>
       </c>
@@ -4767,22 +5223,22 @@
         <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -4791,10 +5247,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>120.28</v>
+        <v>119.29</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.65</v>
+        <v>-0.99</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -4803,90 +5259,60 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B49" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C49" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D49" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E49" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H49" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W49" t="n">
         <v>23.4</v>
       </c>
-      <c r="I49" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K49" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N49" t="n">
-        <v>33</v>
-      </c>
-      <c r="O49" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>23.2</v>
+      <c r="X49" t="n">
+        <v>19.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA49" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>220.58</v>
+        <v>223.43</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.15</v>
+        <v>2.85</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -4895,10 +5321,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>119.29</v>
+        <v>121.35</v>
       </c>
       <c r="AL49" t="n">
-        <v>-0.99</v>
+        <v>2.06</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -4906,52 +5332,55 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B50" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D50" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F50" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X50" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
         <v>13</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AF50" t="n">
-        <v>223.43</v>
+        <v>229.48</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.85</v>
+        <v>6.05</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -4960,10 +5389,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>121.35</v>
+        <v>128.37</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.06</v>
+        <v>7.02</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -4972,45 +5401,93 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B51" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>50.6</v>
       </c>
       <c r="D51" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>19.4</v>
       </c>
       <c r="F51" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>24</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K51" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N51" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W51" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y51" t="n">
         <v>8</v>
       </c>
       <c r="Z51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF51" t="n">
-        <v>229.48</v>
+        <v>241.48</v>
       </c>
       <c r="AG51" t="n">
-        <v>6.05</v>
+        <v>12</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5019,10 +5496,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL51" t="n">
-        <v>7.02</v>
+        <v>6.22</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5030,85 +5507,100 @@
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B52" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C52" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D52" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E52" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H52" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I52" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J52" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K52" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M52" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N52" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O52" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
+      </c>
+      <c r="V52" t="n">
+        <v>12</v>
+      </c>
+      <c r="W52" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X52" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC52" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>241.48</v>
+        <v>238.69</v>
       </c>
       <c r="AG52" t="n">
-        <v>12</v>
+        <v>-2.8</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5117,10 +5609,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL52" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5129,90 +5621,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B53" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C53" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D53" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E53" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F53" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H53" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I53" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J53" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K53" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M53" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N53" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O53" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R53" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
+      </c>
+      <c r="V53" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X53" t="n">
+        <v>19.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA53" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG53" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5221,10 +5722,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5233,90 +5734,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS53" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B54" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C54" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D54" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E54" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F54" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H54" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I54" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K54" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O54" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R54" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
+      </c>
+      <c r="V54" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="W54" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="X54" t="n">
+        <v>20.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z54" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB54" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC54" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF54" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG54" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5325,10 +5835,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL54" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5337,57 +5847,57 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS54" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B55" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C55" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D55" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E55" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F55" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H55" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I55" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J55" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K55" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O55" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5396,31 +5906,40 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>21.6</v>
+        <v>21</v>
+      </c>
+      <c r="V55" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="X55" t="n">
+        <v>21.1</v>
       </c>
       <c r="Y55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA55" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC55" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5429,10 +5948,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>136.33</v>
+        <v>137.17</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5441,90 +5960,42 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS55" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B56" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C56" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D56" t="n">
         <v>35.6</v>
       </c>
-      <c r="E56" t="n">
-        <v>26</v>
-      </c>
       <c r="F56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>24</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J56" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K56" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O56" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>21</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
         <v>19</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.8</v>
+        <v>13</v>
       </c>
       <c r="AF56" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5533,10 +6004,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>137.17</v>
+        <v>136.08</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5544,43 +6015,37 @@
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B57" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D57" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y57" t="n">
         <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5589,10 +6054,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>136.08</v>
+        <v>135.42</v>
       </c>
       <c r="AL57" t="n">
-        <v>-1.09</v>
+        <v>-0.66</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5601,36 +6066,75 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B58" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>28.1</v>
       </c>
       <c r="F58" t="n">
         <v>3.3</v>
       </c>
+      <c r="H58" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N58" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.7</v>
+      </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA58" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF58" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG58" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -5639,10 +6143,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL58" t="n">
-        <v>-0.66</v>
+        <v>-4.18</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -5650,76 +6154,82 @@
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B59" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C59" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E59" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F59" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H59" t="n">
         <v>23.4</v>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K59" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M59" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N59" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O59" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R59" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF59" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG59" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -5728,10 +6238,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL59" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -5740,81 +6250,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B60" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C60" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D60" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E60" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F60" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H60" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I60" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K60" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O60" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R60" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T60" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF60" t="n">
-        <v>218.37</v>
+        <v>220.85</v>
       </c>
       <c r="AG60" t="n">
-        <v>-4.49</v>
+        <v>2.48</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -5823,10 +6333,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL60" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -5835,42 +6345,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS60" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B61" t="n">
         <v>135.8</v>
       </c>
       <c r="D61" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>220.85</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>2.48</v>
+        <v>14.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -5878,12 +6382,6 @@
       <c r="AI61" t="n">
         <v>235</v>
       </c>
-      <c r="AK61" t="n">
-        <v>129.07</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>-0.14</v>
-      </c>
       <c r="AM61" t="n">
         <v>110</v>
       </c>
@@ -5891,30 +6389,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B62" t="n">
-        <v>135.8</v>
+        <v>131.7</v>
       </c>
       <c r="D62" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -5929,7 +6427,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -3693,6 +3693,18 @@
       <c r="BL32" s="1" t="n">
         <v>46245</v>
       </c>
+      <c r="BM32" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4649.3</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>2021.1</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>3016.3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3806,6 +3818,18 @@
       <c r="BL33" s="1" t="n">
         <v>46246</v>
       </c>
+      <c r="BM33" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>6995.8</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>2380.8</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>3192.8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3880,6 +3904,18 @@
       <c r="BL34" s="1" t="n">
         <v>46247</v>
       </c>
+      <c r="BM34" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>2827.2</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>3152.1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3954,6 +3990,18 @@
       <c r="BL35" s="1" t="n">
         <v>46248</v>
       </c>
+      <c r="BM35" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>3609.5</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>1161.2</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>3077.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4028,6 +4076,18 @@
       <c r="BL36" s="1" t="n">
         <v>46249</v>
       </c>
+      <c r="BM36" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>1884.4</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>2636.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4102,6 +4162,18 @@
       <c r="BL37" s="1" t="n">
         <v>46250</v>
       </c>
+      <c r="BM37" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>1894.8</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -4215,6 +4287,18 @@
       <c r="BL38" s="1" t="n">
         <v>46251</v>
       </c>
+      <c r="BM38" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>2723.2</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -4328,6 +4412,18 @@
       <c r="BL39" s="1" t="n">
         <v>46252</v>
       </c>
+      <c r="BM39" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>6652.6</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>1412.3</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>408</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -4441,6 +4537,18 @@
       <c r="BL40" s="1" t="n">
         <v>46253</v>
       </c>
+      <c r="BM40" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>4993.3</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>958.6</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>2899.8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -4554,6 +4662,18 @@
       <c r="BL41" s="1" t="n">
         <v>46254</v>
       </c>
+      <c r="BM41" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1514.9</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>799.7</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>2923.4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4628,6 +4748,18 @@
       <c r="BL42" s="1" t="n">
         <v>46255</v>
       </c>
+      <c r="BM42" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>1526.5</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>957.4</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>2928.4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4702,6 +4834,18 @@
       <c r="BL43" s="1" t="n">
         <v>46256</v>
       </c>
+      <c r="BM43" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>2825.6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4815,6 +4959,18 @@
       <c r="BL44" s="1" t="n">
         <v>46257</v>
       </c>
+      <c r="BM44" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>2769.3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4928,6 +5084,18 @@
       <c r="BL45" s="1" t="n">
         <v>46258</v>
       </c>
+      <c r="BM45" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>2982.8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -5041,6 +5209,18 @@
       <c r="BL46" s="1" t="n">
         <v>46259</v>
       </c>
+      <c r="BM46" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>3194.6</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -5154,6 +5334,18 @@
       <c r="BL47" s="1" t="n">
         <v>46260</v>
       </c>
+      <c r="BM47" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>2717.1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -5267,6 +5459,18 @@
       <c r="BL48" s="1" t="n">
         <v>46261</v>
       </c>
+      <c r="BM48" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>3028.8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -5335,6 +5539,18 @@
       <c r="BL49" s="1" t="n">
         <v>46262</v>
       </c>
+      <c r="BM49" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>2959.2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -5403,6 +5619,18 @@
       <c r="BL50" s="1" t="n">
         <v>46263</v>
       </c>
+      <c r="BM50" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>34</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -5516,6 +5744,18 @@
       <c r="BL51" s="1" t="n">
         <v>46264</v>
       </c>
+      <c r="BM51" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5629,6 +5869,18 @@
       <c r="BL52" s="1" t="n">
         <v>46265</v>
       </c>
+      <c r="BM52" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -5742,6 +5994,18 @@
       <c r="BL53" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="BM53" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5855,6 +6119,18 @@
       <c r="BL54" s="1" t="n">
         <v>46267</v>
       </c>
+      <c r="BM54" t="n">
+        <v>32</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5968,6 +6244,18 @@
       <c r="BL55" s="1" t="n">
         <v>46268</v>
       </c>
+      <c r="BM55" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -6018,6 +6306,18 @@
       <c r="BL56" s="1" t="n">
         <v>46269</v>
       </c>
+      <c r="BM56" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -6068,6 +6368,18 @@
       <c r="BL57" s="1" t="n">
         <v>46270</v>
       </c>
+      <c r="BM57" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -6163,6 +6475,18 @@
       <c r="BL58" s="1" t="n">
         <v>46271</v>
       </c>
+      <c r="BM58" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>249.4</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -6258,6 +6582,18 @@
       <c r="BL59" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="BM59" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>227</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>2758.6</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -6353,6 +6689,18 @@
       <c r="BL60" s="1" t="n">
         <v>46273</v>
       </c>
+      <c r="BM60" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>547</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>85</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>2654.5</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -6390,6 +6738,18 @@
       </c>
       <c r="BL61" s="1" t="n">
         <v>46274</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>124</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>2635.8</v>
       </c>
     </row>
     <row r="62">

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,55 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B2" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C2" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>41.5</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>18</v>
+      </c>
+      <c r="T2" t="n">
+        <v>23</v>
       </c>
       <c r="V2" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W2" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X2" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -685,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -696,94 +729,100 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
+      <c r="AP2" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B3" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C3" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D3" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E3" t="n">
         <v>34.6</v>
       </c>
       <c r="F3" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="n">
         <v>23.9</v>
       </c>
       <c r="I3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J3" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K3" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -792,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -804,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C4" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E4" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F4" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I4" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J4" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K4" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O4" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
         <v>17.6</v>
       </c>
       <c r="T4" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W4" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA4" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -905,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -917,99 +956,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B5" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C5" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E5" t="n">
         <v>30.4</v>
       </c>
-      <c r="E5" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I5" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J5" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O5" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S5" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W5" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y5" t="n">
         <v>17</v>
       </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1018,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1030,99 +1069,66 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B6" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D6" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V6" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W6" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X6" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC6" t="n">
         <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1131,10 +1137,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1142,67 +1148,61 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B7" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D7" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O7" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V7" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W7" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X7" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1223,60 +1223,93 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B8" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31.5</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.1</v>
       </c>
       <c r="K8" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>35</v>
       </c>
       <c r="O8" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W8" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X8" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1285,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1296,94 +1329,100 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
+      <c r="AP8" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B9" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I9" t="n">
         <v>11.4</v>
       </c>
       <c r="J9" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K9" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O9" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T9" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X9" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1392,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL9" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1404,99 +1443,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B10" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C10" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D10" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA10" t="n">
         <v>11.4</v>
       </c>
-      <c r="J10" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>76</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>14</v>
-      </c>
-      <c r="T10" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB10" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF10" t="n">
         <v>220.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1505,10 +1544,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1517,99 +1556,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B11" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C11" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E11" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I11" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J11" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K11" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O11" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF11" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1618,10 +1657,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1630,99 +1669,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B12" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C12" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D12" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E12" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H12" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I12" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J12" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K12" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O12" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T12" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W12" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X12" t="n">
         <v>12.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
         <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF12" t="n">
         <v>216.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1731,10 +1770,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL12" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1743,99 +1782,66 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B13" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D13" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F13" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N13" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V13" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X13" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1844,10 +1850,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1855,67 +1861,61 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B14" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D14" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>6.8</v>
       </c>
       <c r="K14" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O14" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
         <v>13.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1924,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1936,60 +1936,93 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B15" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25.9</v>
       </c>
       <c r="F15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>38.8</v>
       </c>
       <c r="K15" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>36.7</v>
       </c>
       <c r="O15" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21.7</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W15" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X15" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1998,10 +2031,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2009,94 +2042,67 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B16" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
-      </c>
-      <c r="E16" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>24</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O16" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V16" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X16" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,10 +2111,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2116,67 +2122,94 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B17" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>63.7</v>
       </c>
       <c r="D17" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>36.4</v>
       </c>
       <c r="F17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>39.9</v>
       </c>
       <c r="K17" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>35.9</v>
       </c>
       <c r="O17" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>20.3</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W17" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X17" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2185,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2196,94 +2229,100 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B18" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C18" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E18" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F18" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H18" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I18" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J18" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K18" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N18" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O18" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X18" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2292,10 +2331,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2304,99 +2343,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B19" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C19" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E19" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F19" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I19" t="n">
         <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K19" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O19" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V19" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X19" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2405,10 +2444,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL19" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2417,99 +2456,66 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B20" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D20" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K20" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O20" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V20" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X20" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB20" t="n">
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2518,10 +2524,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2529,67 +2535,61 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B21" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O21" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V21" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y21" t="n">
         <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2598,10 +2598,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2610,60 +2610,93 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B22" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>56.3</v>
       </c>
       <c r="D22" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>21.2</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>40.4</v>
       </c>
       <c r="K22" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29</v>
       </c>
       <c r="O22" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W22" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X22" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2672,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL22" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2683,52 +2716,58 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B23" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C23" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D23" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H23" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J23" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K23" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O23" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
@@ -2737,40 +2776,40 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V23" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W23" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X23" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG23" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2779,10 +2818,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2791,99 +2830,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS23" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B24" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C24" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E24" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I24" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K24" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O24" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W24" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X24" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2892,10 +2931,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL24" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2904,99 +2943,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B25" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C25" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D25" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F25" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H25" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J25" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K25" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N25" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O25" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q25" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V25" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W25" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3005,10 +3044,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL25" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3017,99 +3056,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B26" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C26" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E26" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I26" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J26" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K26" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N26" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O26" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V26" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W26" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X26" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3118,10 +3157,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3130,99 +3169,60 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B27" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C27" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D27" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K27" t="n">
-        <v>77</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>21</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X27" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA27" t="n">
         <v>9</v>
       </c>
-      <c r="Z27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB27" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3231,10 +3231,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3242,61 +3242,61 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B28" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D28" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F28" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>35.5</v>
       </c>
       <c r="V28" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W28" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="n">
         <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3305,10 +3305,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3317,60 +3317,60 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B29" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D29" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O29" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V29" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X29" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3379,10 +3379,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3391,60 +3391,93 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B30" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>86.8</v>
       </c>
       <c r="D30" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>33</v>
       </c>
       <c r="F30" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>41.1</v>
       </c>
       <c r="K30" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33.5</v>
       </c>
       <c r="O30" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="n">
+        <v>22.4</v>
       </c>
       <c r="V30" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X30" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3453,10 +3486,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3464,94 +3497,100 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B31" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C31" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D31" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E31" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F31" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H31" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I31" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J31" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K31" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O31" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R31" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T31" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X31" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z31" t="n">
         <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB31" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG31" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3560,10 +3599,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3572,99 +3611,111 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>4649.3</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>2021.1</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>3016.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B32" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C32" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D32" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E32" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F32" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I32" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J32" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K32" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O32" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R32" t="n">
         <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T32" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V32" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W32" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X32" t="n">
         <v>10.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB32" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD32" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF32" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG32" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3673,10 +3724,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL32" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3685,111 +3736,78 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="BM32" t="n">
-        <v>40.72</v>
+        <v>40.4</v>
       </c>
       <c r="BN32" t="n">
-        <v>4649.3</v>
+        <v>6995.8</v>
       </c>
       <c r="BO32" t="n">
-        <v>2021.1</v>
+        <v>2380.8</v>
       </c>
       <c r="BP32" t="n">
-        <v>3016.3</v>
+        <v>3192.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B33" t="n">
-        <v>183</v>
-      </c>
-      <c r="C33" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D33" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E33" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K33" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O33" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T33" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V33" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W33" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X33" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
         <v>10</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3798,10 +3816,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL33" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3809,79 +3827,73 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="BM33" t="n">
-        <v>40.4</v>
+        <v>39.65</v>
       </c>
       <c r="BN33" t="n">
-        <v>6995.8</v>
+        <v>2827.2</v>
       </c>
       <c r="BO33" t="n">
-        <v>2380.8</v>
+        <v>2051.2</v>
       </c>
       <c r="BP33" t="n">
-        <v>3192.8</v>
+        <v>3152.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B34" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F34" t="n">
         <v>6.5</v>
       </c>
       <c r="K34" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O34" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V34" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X34" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3890,10 +3902,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3902,72 +3914,72 @@
         <v>142</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="BM34" t="n">
-        <v>39.65</v>
+        <v>34.79</v>
       </c>
       <c r="BN34" t="n">
-        <v>2827.2</v>
+        <v>3609.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>2051.2</v>
+        <v>1161.2</v>
       </c>
       <c r="BP34" t="n">
-        <v>3152.1</v>
+        <v>3077.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B35" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F35" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K35" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O35" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V35" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X35" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3976,10 +3988,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>116.37</v>
+        <v>120.64</v>
       </c>
       <c r="AL35" t="n">
-        <v>-0.15</v>
+        <v>4.27</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3988,72 +4000,72 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="BM35" t="n">
-        <v>34.79</v>
+        <v>31.22</v>
       </c>
       <c r="BN35" t="n">
-        <v>3609.5</v>
+        <v>1884.4</v>
       </c>
       <c r="BO35" t="n">
-        <v>1161.2</v>
+        <v>785.2</v>
       </c>
       <c r="BP35" t="n">
-        <v>3077.1</v>
+        <v>2636.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B36" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D36" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F36" t="n">
         <v>5.5</v>
       </c>
       <c r="K36" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O36" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V36" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X36" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA36" t="n">
         <v>15</v>
       </c>
-      <c r="AA36" t="n">
-        <v>14</v>
-      </c>
       <c r="AB36" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF36" t="n">
-        <v>225.14</v>
+        <v>229.98</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.15</v>
+        <v>4.84</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4062,10 +4074,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>120.64</v>
+        <v>128.14</v>
       </c>
       <c r="AL36" t="n">
-        <v>4.27</v>
+        <v>7.5</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4074,72 +4086,105 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="BM36" t="n">
-        <v>31.22</v>
+        <v>26.41</v>
       </c>
       <c r="BN36" t="n">
-        <v>1884.4</v>
+        <v>1894.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>785.2</v>
+        <v>223.6</v>
       </c>
       <c r="BP36" t="n">
-        <v>2636.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B37" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C37" t="n">
+        <v>71.8</v>
       </c>
       <c r="D37" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E37" t="n">
+        <v>24.7</v>
       </c>
       <c r="F37" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41.1</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>33.5</v>
       </c>
       <c r="O37" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>23.2</v>
       </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W37" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X37" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y37" t="n">
         <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>229.98</v>
+        <v>229.96</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.84</v>
+        <v>-0.02</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4148,10 +4193,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL37" t="n">
-        <v>7.5</v>
+        <v>0.01</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4159,17 +4204,23 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="BM37" t="n">
-        <v>26.41</v>
+        <v>29.83</v>
       </c>
       <c r="BN37" t="n">
-        <v>1894.8</v>
+        <v>2723.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>223.6</v>
+        <v>271.1</v>
       </c>
       <c r="BP37" t="n">
         <v>0</v>
@@ -4177,88 +4228,88 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B38" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C38" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D38" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E38" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H38" t="n">
         <v>24.1</v>
       </c>
       <c r="I38" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J38" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K38" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O38" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V38" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W38" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z38" t="n">
         <v>13</v>
       </c>
-      <c r="X38" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>14</v>
-      </c>
       <c r="AA38" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4267,10 +4318,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4279,111 +4330,111 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS38" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="BM38" t="n">
-        <v>29.83</v>
+        <v>33.62</v>
       </c>
       <c r="BN38" t="n">
-        <v>2723.2</v>
+        <v>6652.6</v>
       </c>
       <c r="BO38" t="n">
-        <v>271.1</v>
+        <v>1412.3</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B39" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C39" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D39" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E39" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H39" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I39" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K39" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O39" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R39" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V39" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W39" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X39" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG39" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4392,10 +4443,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4404,111 +4455,111 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS39" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="BM39" t="n">
-        <v>33.62</v>
+        <v>32.38</v>
       </c>
       <c r="BN39" t="n">
-        <v>6652.6</v>
+        <v>4993.3</v>
       </c>
       <c r="BO39" t="n">
-        <v>1412.3</v>
+        <v>958.6</v>
       </c>
       <c r="BP39" t="n">
-        <v>408</v>
+        <v>2899.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B40" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C40" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D40" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F40" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H40" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I40" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J40" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K40" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N40" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O40" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T40" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V40" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W40" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X40" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA40" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4517,10 +4568,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>130.88</v>
+        <v>132.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4529,111 +4580,78 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="BM40" t="n">
-        <v>32.38</v>
+        <v>33.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>4993.3</v>
+        <v>1514.9</v>
       </c>
       <c r="BO40" t="n">
-        <v>958.6</v>
+        <v>799.7</v>
       </c>
       <c r="BP40" t="n">
-        <v>2899.8</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B41" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C41" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D41" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H41" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K41" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V41" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W41" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X41" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC41" t="n">
         <v>8.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4642,10 +4660,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>132.55</v>
+        <v>128.02</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.67</v>
+        <v>-4.53</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4653,79 +4671,73 @@
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="BM41" t="n">
-        <v>33.01</v>
+        <v>35.62</v>
       </c>
       <c r="BN41" t="n">
-        <v>1514.9</v>
+        <v>1526.5</v>
       </c>
       <c r="BO41" t="n">
-        <v>799.7</v>
+        <v>957.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>2923.4</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B42" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F42" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K42" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O42" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V42" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W42" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X42" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
         <v>9</v>
       </c>
       <c r="AB42" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF42" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG42" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4734,10 +4746,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>128.02</v>
+        <v>127.06</v>
       </c>
       <c r="AL42" t="n">
-        <v>-4.53</v>
+        <v>-0.96</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4746,72 +4758,105 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="BM42" t="n">
-        <v>35.62</v>
+        <v>34.56</v>
       </c>
       <c r="BN42" t="n">
-        <v>1526.5</v>
+        <v>170.6</v>
       </c>
       <c r="BO42" t="n">
-        <v>957.4</v>
+        <v>130.4</v>
       </c>
       <c r="BP42" t="n">
-        <v>2928.4</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B43" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>73.7</v>
       </c>
       <c r="D43" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E43" t="n">
+        <v>28.2</v>
       </c>
       <c r="F43" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>40.1</v>
       </c>
       <c r="K43" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N43" t="n">
+        <v>32.9</v>
       </c>
       <c r="O43" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23.5</v>
       </c>
       <c r="V43" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W43" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X43" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y43" t="n">
         <v>4</v>
       </c>
       <c r="Z43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4820,10 +4865,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.96</v>
+        <v>-1.45</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4831,106 +4876,112 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="BM43" t="n">
-        <v>34.56</v>
+        <v>34.78</v>
       </c>
       <c r="BN43" t="n">
-        <v>170.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO43" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>2825.6</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B44" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C44" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E44" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F44" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H44" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I44" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J44" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K44" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M44" t="n">
         <v>6.8</v>
       </c>
       <c r="N44" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O44" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R44" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T44" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V44" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W44" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X44" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z44" t="n">
         <v>13</v>
       </c>
       <c r="AA44" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC44" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB44" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD44" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4939,10 +4990,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL44" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4951,111 +5002,111 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS44" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="BM44" t="n">
-        <v>34.78</v>
+        <v>36.78</v>
       </c>
       <c r="BN44" t="n">
-        <v>69.59999999999999</v>
+        <v>108.8</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>204.3</v>
       </c>
       <c r="BP44" t="n">
-        <v>2769.3</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B45" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C45" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E45" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I45" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J45" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K45" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M45" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N45" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O45" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q45" t="n">
         <v>23.1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S45" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T45" t="n">
         <v>23.1</v>
       </c>
       <c r="V45" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W45" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X45" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA45" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG45" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5064,10 +5115,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5076,111 +5127,111 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="BM45" t="n">
-        <v>36.78</v>
+        <v>32.64</v>
       </c>
       <c r="BN45" t="n">
-        <v>108.8</v>
+        <v>42.3</v>
       </c>
       <c r="BO45" t="n">
-        <v>204.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP45" t="n">
-        <v>2982.8</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B46" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C46" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E46" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F46" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H46" t="n">
         <v>23.8</v>
       </c>
       <c r="I46" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J46" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O46" t="n">
         <v>40.1</v>
       </c>
-      <c r="K46" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O46" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q46" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S46" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC46" t="n">
         <v>9.6</v>
       </c>
-      <c r="W46" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD46" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5189,10 +5240,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL46" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5201,87 +5252,87 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS46" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="BM46" t="n">
-        <v>32.64</v>
+        <v>29.61</v>
       </c>
       <c r="BN46" t="n">
-        <v>42.3</v>
+        <v>60.1</v>
       </c>
       <c r="BO46" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP46" t="n">
-        <v>3194.6</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B47" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C47" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D47" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E47" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F47" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H47" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I47" t="n">
         <v>7.2</v>
       </c>
       <c r="J47" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K47" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M47" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N47" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O47" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q47" t="n">
         <v>23.2</v>
       </c>
       <c r="R47" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
         <v>23.2</v>
       </c>
       <c r="V47" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W47" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X47" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -5290,22 +5341,22 @@
         <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5314,10 +5365,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>120.28</v>
+        <v>119.29</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.65</v>
+        <v>-0.99</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5326,111 +5377,72 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="BM47" t="n">
-        <v>29.61</v>
+        <v>31.11</v>
       </c>
       <c r="BN47" t="n">
-        <v>60.1</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP47" t="n">
-        <v>2717.1</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B48" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C48" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D48" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E48" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H48" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W48" t="n">
         <v>23.4</v>
       </c>
-      <c r="I48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K48" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M48" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N48" t="n">
-        <v>33</v>
-      </c>
-      <c r="O48" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V48" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X48" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA48" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF48" t="n">
-        <v>220.58</v>
+        <v>223.43</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.15</v>
+        <v>2.85</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5439,10 +5451,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>119.29</v>
+        <v>121.35</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.99</v>
+        <v>2.06</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5450,73 +5462,67 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="BM48" t="n">
-        <v>31.11</v>
+        <v>30.59</v>
       </c>
       <c r="BN48" t="n">
-        <v>87.90000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="BO48" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP48" t="n">
-        <v>3028.8</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B49" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D49" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F49" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V49" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W49" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X49" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
         <v>13</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AF49" t="n">
-        <v>223.43</v>
+        <v>229.48</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.85</v>
+        <v>6.05</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5525,10 +5531,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>121.35</v>
+        <v>128.37</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.06</v>
+        <v>7.02</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5537,66 +5543,105 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="BM49" t="n">
-        <v>30.59</v>
+        <v>30.05</v>
       </c>
       <c r="BN49" t="n">
-        <v>40.8</v>
+        <v>34</v>
       </c>
       <c r="BO49" t="n">
         <v>0</v>
       </c>
       <c r="BP49" t="n">
-        <v>2959.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B50" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>50.6</v>
       </c>
       <c r="D50" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>19.4</v>
       </c>
       <c r="F50" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>24</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N50" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>21.4</v>
       </c>
       <c r="V50" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W50" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X50" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y50" t="n">
         <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF50" t="n">
-        <v>229.48</v>
+        <v>241.48</v>
       </c>
       <c r="AG50" t="n">
-        <v>6.05</v>
+        <v>12</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5605,10 +5650,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL50" t="n">
-        <v>7.02</v>
+        <v>6.22</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5616,14 +5661,20 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="BM50" t="n">
-        <v>30.05</v>
+        <v>24.86</v>
       </c>
       <c r="BN50" t="n">
-        <v>34</v>
+        <v>80.2</v>
       </c>
       <c r="BO50" t="n">
         <v>0</v>
@@ -5634,88 +5685,88 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B51" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C51" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D51" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E51" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F51" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I51" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J51" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K51" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M51" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N51" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O51" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V51" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W51" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X51" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC51" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>241.48</v>
+        <v>238.69</v>
       </c>
       <c r="AG51" t="n">
-        <v>12</v>
+        <v>-2.8</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5724,10 +5775,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL51" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5736,19 +5787,19 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="BM51" t="n">
-        <v>24.86</v>
+        <v>29.8</v>
       </c>
       <c r="BN51" t="n">
-        <v>80.2</v>
+        <v>61.9</v>
       </c>
       <c r="BO51" t="n">
         <v>0</v>
@@ -5759,88 +5810,88 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B52" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C52" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D52" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E52" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F52" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H52" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I52" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J52" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K52" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M52" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N52" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O52" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V52" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W52" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X52" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA52" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC52" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG52" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5849,10 +5900,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5861,19 +5912,19 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS52" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="BM52" t="n">
-        <v>29.8</v>
+        <v>36.03</v>
       </c>
       <c r="BN52" t="n">
-        <v>61.9</v>
+        <v>76.5</v>
       </c>
       <c r="BO52" t="n">
         <v>0</v>
@@ -5884,88 +5935,88 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B53" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C53" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D53" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E53" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F53" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H53" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I53" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K53" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O53" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R53" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V53" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W53" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X53" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF53" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG53" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5974,10 +6025,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL53" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5986,19 +6037,19 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS53" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="BM53" t="n">
-        <v>36.03</v>
+        <v>32</v>
       </c>
       <c r="BN53" t="n">
-        <v>76.5</v>
+        <v>29.5</v>
       </c>
       <c r="BO53" t="n">
         <v>0</v>
@@ -6009,46 +6060,46 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B54" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C54" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D54" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E54" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F54" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H54" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I54" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J54" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K54" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N54" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O54" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -6057,40 +6108,40 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V54" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W54" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X54" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6099,10 +6150,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>136.33</v>
+        <v>137.17</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -6111,19 +6162,19 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS54" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="BM54" t="n">
-        <v>32</v>
+        <v>32.57</v>
       </c>
       <c r="BN54" t="n">
-        <v>29.5</v>
+        <v>23.4</v>
       </c>
       <c r="BO54" t="n">
         <v>0</v>
@@ -6134,88 +6185,49 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B55" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C55" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D55" t="n">
         <v>35.6</v>
       </c>
-      <c r="E55" t="n">
-        <v>26</v>
-      </c>
       <c r="F55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H55" t="n">
-        <v>24</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J55" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K55" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N55" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O55" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>21</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W55" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X55" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y55" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z55" t="n">
         <v>19</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB55" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF55" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6224,10 +6236,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>137.17</v>
+        <v>136.08</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -6235,20 +6247,14 @@
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="BM55" t="n">
-        <v>32.57</v>
+        <v>29.64</v>
       </c>
       <c r="BN55" t="n">
-        <v>23.4</v>
+        <v>36.4</v>
       </c>
       <c r="BO55" t="n">
         <v>0</v>
@@ -6259,31 +6265,31 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B56" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D56" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y56" t="n">
         <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6292,10 +6298,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>136.08</v>
+        <v>135.42</v>
       </c>
       <c r="AL56" t="n">
-        <v>-1.09</v>
+        <v>-0.66</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -6304,13 +6310,13 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="BM56" t="n">
-        <v>29.64</v>
+        <v>31.45</v>
       </c>
       <c r="BN56" t="n">
-        <v>36.4</v>
+        <v>35.9</v>
       </c>
       <c r="BO56" t="n">
         <v>0</v>
@@ -6321,31 +6327,70 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B57" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C57" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>28.1</v>
       </c>
       <c r="F57" t="n">
         <v>3.3</v>
       </c>
+      <c r="H57" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9</v>
+      </c>
+      <c r="J57" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N57" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23.7</v>
+      </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF57" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG57" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6354,10 +6399,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL57" t="n">
-        <v>-0.66</v>
+        <v>-4.18</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6365,88 +6410,94 @@
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="BM57" t="n">
-        <v>31.45</v>
+        <v>34.46</v>
       </c>
       <c r="BN57" t="n">
-        <v>35.9</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO57" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP57" t="n">
-        <v>0</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B58" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C58" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E58" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F58" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H58" t="n">
         <v>23.4</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K58" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M58" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N58" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O58" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R58" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z58" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF58" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG58" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6455,10 +6506,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL58" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6467,93 +6518,93 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS58" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="BM58" t="n">
-        <v>34.46</v>
+        <v>35.4</v>
       </c>
       <c r="BN58" t="n">
-        <v>80.40000000000001</v>
+        <v>294.2</v>
       </c>
       <c r="BO58" t="n">
-        <v>373.6</v>
+        <v>227</v>
       </c>
       <c r="BP58" t="n">
-        <v>249.4</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B59" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C59" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D59" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E59" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F59" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H59" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I59" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K59" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N59" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O59" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R59" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T59" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA59" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>218.37</v>
+        <v>220.85</v>
       </c>
       <c r="AG59" t="n">
-        <v>-4.49</v>
+        <v>2.48</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6562,10 +6613,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL59" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6574,93 +6625,93 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS59" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="BM59" t="n">
-        <v>35.4</v>
+        <v>32.31</v>
       </c>
       <c r="BN59" t="n">
-        <v>294.2</v>
+        <v>547</v>
       </c>
       <c r="BO59" t="n">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="BP59" t="n">
-        <v>2758.6</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B60" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C60" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E60" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F60" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H60" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J60" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K60" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N60" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O60" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q60" t="n">
         <v>21.7</v>
       </c>
       <c r="R60" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S60" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>21.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA60" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AF60" t="n">
-        <v>220.85</v>
+        <v>220.84</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.48</v>
+        <v>-0.01</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6669,10 +6720,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL60" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6681,48 +6732,48 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="BM60" t="n">
-        <v>32.31</v>
+        <v>31.51</v>
       </c>
       <c r="BN60" t="n">
-        <v>547</v>
+        <v>124</v>
       </c>
       <c r="BO60" t="n">
-        <v>85</v>
+        <v>164.4</v>
       </c>
       <c r="BP60" t="n">
-        <v>2654.5</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B61" t="n">
-        <v>135.8</v>
+        <v>131.7</v>
       </c>
       <c r="D61" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6737,42 +6788,42 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="BM61" t="n">
-        <v>31.51</v>
+        <v>34.36</v>
       </c>
       <c r="BN61" t="n">
-        <v>124</v>
+        <v>62.8</v>
       </c>
       <c r="BO61" t="n">
-        <v>164.4</v>
+        <v>60.6</v>
       </c>
       <c r="BP61" t="n">
-        <v>2635.8</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B62" t="n">
-        <v>131.7</v>
+        <v>133.9</v>
       </c>
       <c r="D62" t="n">
-        <v>33.2</v>
+        <v>34.7</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6787,7 +6838,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -6781,6 +6781,12 @@
       <c r="AI61" t="n">
         <v>235</v>
       </c>
+      <c r="AK61" t="n">
+        <v>132</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>1.27</v>
+      </c>
       <c r="AM61" t="n">
         <v>110</v>
       </c>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -6276,6 +6276,15 @@
       <c r="F56" t="n">
         <v>3.3</v>
       </c>
+      <c r="V56" t="n">
+        <v>11</v>
+      </c>
+      <c r="W56" t="n">
+        <v>22</v>
+      </c>
+      <c r="X56" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y56" t="n">
         <v>7</v>
       </c>
@@ -6284,6 +6293,15 @@
       </c>
       <c r="AA56" t="n">
         <v>10.5</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.4</v>
       </c>
       <c r="AF56" t="n">
         <v>229.75</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -6784,6 +6784,21 @@
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
+      <c r="H61" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N61" t="n">
+        <v>33.1</v>
+      </c>
       <c r="Y61" t="n">
         <v>11</v>
       </c>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="B2" t="n">
-        <v>183.5</v>
+        <v>179.6</v>
       </c>
       <c r="C2" t="n">
-        <v>84.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>34.6</v>
+        <v>31.1</v>
       </c>
       <c r="F2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
-        <v>23.9</v>
+        <v>21.5</v>
       </c>
       <c r="I2" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="J2" t="n">
-        <v>41.5</v>
+        <v>42.3</v>
       </c>
       <c r="K2" t="n">
-        <v>76.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N2" t="n">
-        <v>37.7</v>
+        <v>37.1</v>
       </c>
       <c r="O2" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>21.2</v>
       </c>
       <c r="T2" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="V2" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="X2" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.7</v>
+        <v>11.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>220.36</v>
+        <v>216.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.75</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>127.13</v>
+        <v>127.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.21</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>76.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.17</v>
+        <v>15.16</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46216</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="B3" t="n">
-        <v>180.5</v>
+        <v>170.4</v>
       </c>
       <c r="C3" t="n">
-        <v>79.2</v>
+        <v>78.5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.7</v>
+        <v>29.8</v>
       </c>
       <c r="E3" t="n">
-        <v>34.6</v>
+        <v>29.7</v>
       </c>
       <c r="F3" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="I3" t="n">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="J3" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="K3" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
-        <v>37.7</v>
+        <v>36.6</v>
       </c>
       <c r="O3" t="n">
-        <v>42.7</v>
+        <v>41.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>17.6</v>
+        <v>21.1</v>
       </c>
       <c r="T3" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V3" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>20.8</v>
+        <v>15.7</v>
       </c>
       <c r="X3" t="n">
-        <v>14.9</v>
+        <v>12.6</v>
       </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>219.64</v>
+        <v>216.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>126.03</v>
+        <v>128.54</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,66 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>82.95</v>
+        <v>84.73</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.55</v>
+        <v>15.34</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46217</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="B4" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>69.7</v>
+        <v>156</v>
       </c>
       <c r="D4" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>33.9</v>
+        <v>30.1</v>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41.2</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M4" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD4" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>224.93</v>
+        <v>224.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>129.28</v>
+        <v>130.92</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -955,100 +922,61 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
-      <c r="AP4" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15.25</v>
-      </c>
       <c r="BL4" s="1" t="n">
-        <v>46218</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46219</v>
+        <v>46228</v>
       </c>
       <c r="B5" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>58.8</v>
+        <v>147.8</v>
       </c>
       <c r="D5" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30.4</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41</v>
+        <v>6.8</v>
       </c>
       <c r="K5" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>37.8</v>
+        <v>96.5</v>
       </c>
       <c r="O5" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21.5</v>
+        <v>39.3</v>
       </c>
       <c r="V5" t="n">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>26</v>
+        <v>22.4</v>
       </c>
       <c r="X5" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.3</v>
+        <v>13.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>232.31</v>
+        <v>230.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.67</v>
+        <v>5.74</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +985,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>134.44</v>
+        <v>132.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.16</v>
+        <v>1.84</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1068,67 +996,94 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
-      <c r="AP5" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL5" s="1" t="n">
-        <v>46219</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46220</v>
+        <v>46229</v>
       </c>
       <c r="B6" t="n">
-        <v>136.7</v>
+        <v>149.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>30.7</v>
+        <v>29</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.9</v>
       </c>
       <c r="F6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.8</v>
       </c>
       <c r="K6" t="n">
-        <v>92.59999999999999</v>
+        <v>74.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36.7</v>
       </c>
       <c r="O6" t="n">
-        <v>39.2</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>21.7</v>
       </c>
       <c r="V6" t="n">
-        <v>17.1</v>
+        <v>10.3</v>
       </c>
       <c r="W6" t="n">
-        <v>36.1</v>
+        <v>24.4</v>
       </c>
       <c r="X6" t="n">
-        <v>26.6</v>
+        <v>17.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.7</v>
+        <v>-0.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>235.4</v>
+        <v>237.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.09</v>
+        <v>7.16</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1137,10 +1092,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>137.5</v>
+        <v>134.95</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.06</v>
+        <v>2.19</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1148,61 +1103,67 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46220</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46221</v>
+        <v>46230</v>
       </c>
       <c r="B7" t="n">
-        <v>138.5</v>
+        <v>143.9</v>
       </c>
       <c r="D7" t="n">
-        <v>31.7</v>
+        <v>32.9</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>91</v>
+        <v>96.2</v>
       </c>
       <c r="O7" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="V7" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>22.5</v>
+        <v>25.6</v>
       </c>
       <c r="X7" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>231.99</v>
+        <v>236.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.41</v>
+        <v>-1.29</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,10 +1172,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>136.12</v>
+        <v>136.28</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1223,93 +1184,93 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46221</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46222</v>
+        <v>46231</v>
       </c>
       <c r="B8" t="n">
-        <v>161.1</v>
+        <v>166.4</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>63.7</v>
       </c>
       <c r="D8" t="n">
-        <v>31.9</v>
+        <v>34.5</v>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>36.4</v>
       </c>
       <c r="F8" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="I8" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="J8" t="n">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
       <c r="K8" t="n">
-        <v>75.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="O8" t="n">
-        <v>37.2</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V8" t="n">
-        <v>14.1</v>
+        <v>11.9</v>
       </c>
       <c r="W8" t="n">
-        <v>19.3</v>
+        <v>27</v>
       </c>
       <c r="X8" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>225.51</v>
+        <v>236.13</v>
       </c>
       <c r="AG8" t="n">
-        <v>-6.48</v>
+        <v>-0.01</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1279,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.83</v>
+        <v>134.54</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2.29</v>
+        <v>-1.74</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1291,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>82.93000000000001</v>
+        <v>82.27</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.73</v>
+        <v>16.28</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46222</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="B9" t="n">
-        <v>176.4</v>
+        <v>172.9</v>
       </c>
       <c r="C9" t="n">
-        <v>77.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>32.7</v>
+        <v>34.9</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H9" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="I9" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="J9" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>76.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="N9" t="n">
-        <v>36.4</v>
+        <v>34.8</v>
       </c>
       <c r="O9" t="n">
-        <v>39.1</v>
+        <v>37.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.3</v>
+        <v>19</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>22.3</v>
+        <v>19</v>
       </c>
       <c r="V9" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="W9" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>16.6</v>
       </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5.6</v>
+        <v>-4.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>220.92</v>
+        <v>218.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>-4.59</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1392,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>131.85</v>
+        <v>130.39</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1443,99 +1404,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>79.75</v>
+        <v>78.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.49</v>
+        <v>15.79</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46223</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46224</v>
+        <v>46233</v>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>157.5</v>
       </c>
       <c r="C10" t="n">
-        <v>80.7</v>
+        <v>68.5</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="E10" t="n">
-        <v>35.1</v>
+        <v>27.7</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
-        <v>22.8</v>
+        <v>23.4</v>
       </c>
       <c r="I10" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="J10" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="K10" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N10" t="n">
-        <v>36.9</v>
+        <v>34.9</v>
       </c>
       <c r="O10" t="n">
-        <v>39.8</v>
+        <v>37.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20.5</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="V10" t="n">
-        <v>10.6</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
-        <v>13</v>
+        <v>23.1</v>
       </c>
       <c r="X10" t="n">
-        <v>11.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.4</v>
+        <v>13.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6.1</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.9</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>220.92</v>
+        <v>218.84</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1544,10 +1505,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>130.06</v>
+        <v>133.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.79</v>
+        <v>2.7</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1556,99 +1517,66 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>79.94</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.93</v>
+        <v>15.63</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46224</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="B11" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>81.90000000000001</v>
+        <v>137.6</v>
       </c>
       <c r="D11" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>31.1</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K11" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>37.1</v>
+        <v>96.7</v>
       </c>
       <c r="O11" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>22.6</v>
+        <v>35.1</v>
       </c>
       <c r="V11" t="n">
-        <v>9.6</v>
+        <v>13.6</v>
       </c>
       <c r="W11" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="X11" t="n">
-        <v>12.6</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.1</v>
+        <v>17.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.4</v>
+        <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>216.02</v>
+        <v>221.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1657,10 +1585,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>127.85</v>
+        <v>138.76</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.21</v>
+        <v>5.67</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1668,100 +1596,61 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>15.16</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46225</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46226</v>
+        <v>46235</v>
       </c>
       <c r="B12" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>78.5</v>
+        <v>132.5</v>
       </c>
       <c r="D12" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29.7</v>
+        <v>33.6</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>75</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>36.6</v>
+        <v>97.8</v>
       </c>
       <c r="O12" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>23.3</v>
+        <v>31.6</v>
       </c>
       <c r="V12" t="n">
-        <v>9.5</v>
+        <v>14.8</v>
       </c>
       <c r="W12" t="n">
-        <v>15.7</v>
+        <v>24.7</v>
       </c>
       <c r="X12" t="n">
-        <v>12.6</v>
+        <v>19.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.7</v>
+        <v>16.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>216.02</v>
+        <v>224.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1770,10 +1659,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.54</v>
+        <v>143.55</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.79</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1781,43 +1670,70 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46226</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="B13" t="n">
-        <v>156</v>
+        <v>137.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>56.3</v>
       </c>
       <c r="D13" t="n">
-        <v>30.1</v>
+        <v>32.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>21.2</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>40.4</v>
       </c>
       <c r="K13" t="n">
-        <v>95.90000000000001</v>
+        <v>75.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>29</v>
       </c>
       <c r="O13" t="n">
-        <v>39.2</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>21.6</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="W13" t="n">
-        <v>20.9</v>
+        <v>24.3</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
         <v>12</v>
@@ -1826,22 +1742,22 @@
         <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.2</v>
+        <v>0.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>224.53</v>
+        <v>232.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>7.43</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1850,10 +1766,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>130.92</v>
+        <v>143.61</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>0.06</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1861,61 +1777,100 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46228</v>
+        <v>46237</v>
       </c>
       <c r="B14" t="n">
-        <v>147.8</v>
+        <v>157.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>59.6</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30.6</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>38.9</v>
       </c>
       <c r="K14" t="n">
-        <v>96.5</v>
+        <v>74.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>33.4</v>
       </c>
       <c r="O14" t="n">
-        <v>39.3</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>21.1</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>22.4</v>
+        <v>26.3</v>
       </c>
       <c r="X14" t="n">
-        <v>15.2</v>
+        <v>19.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
         <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>230.27</v>
+        <v>229.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.74</v>
+        <v>-2.53</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1924,10 +1879,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>132.76</v>
+        <v>136.96</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.84</v>
+        <v>-6.65</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1935,94 +1890,100 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46228</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
       <c r="B15" t="n">
-        <v>149.1</v>
+        <v>159.6</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>34.5</v>
       </c>
       <c r="E15" t="n">
-        <v>25.9</v>
+        <v>31.1</v>
       </c>
       <c r="F15" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="H15" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I15" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="J15" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="K15" t="n">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>36.7</v>
+        <v>34.3</v>
       </c>
       <c r="O15" t="n">
-        <v>40.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="V15" t="n">
-        <v>10.3</v>
+        <v>17.5</v>
       </c>
       <c r="W15" t="n">
-        <v>24.4</v>
+        <v>22.5</v>
       </c>
       <c r="X15" t="n">
-        <v>17.4</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>237.43</v>
+        <v>228.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.16</v>
+        <v>-1.14</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2031,10 +1992,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>134.95</v>
+        <v>133.01</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.19</v>
+        <v>-3.95</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2043,66 +2004,99 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>91.28</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46229</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="B16" t="n">
-        <v>143.9</v>
+        <v>160.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>62.6</v>
       </c>
       <c r="D16" t="n">
-        <v>32.9</v>
+        <v>35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32.2</v>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41.1</v>
       </c>
       <c r="K16" t="n">
-        <v>96.2</v>
+        <v>75.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>32.6</v>
       </c>
       <c r="O16" t="n">
-        <v>37.9</v>
+        <v>38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>20.9</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>16.4</v>
       </c>
       <c r="W16" t="n">
-        <v>25.6</v>
+        <v>22.8</v>
       </c>
       <c r="X16" t="n">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>16</v>
+        <v>14.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>236.14</v>
+        <v>225.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.29</v>
+        <v>-3.5</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2111,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>136.28</v>
+        <v>135.24</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.33</v>
+        <v>2.23</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2122,94 +2116,100 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>15.4</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46231</v>
+        <v>46240</v>
       </c>
       <c r="B17" t="n">
-        <v>166.4</v>
+        <v>161.7</v>
       </c>
       <c r="C17" t="n">
-        <v>63.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E17" t="n">
-        <v>36.4</v>
+        <v>27.3</v>
       </c>
       <c r="F17" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="H17" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="I17" t="n">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="J17" t="n">
-        <v>39.9</v>
+        <v>42.6</v>
       </c>
       <c r="K17" t="n">
-        <v>75.2</v>
+        <v>77</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>35.9</v>
+        <v>31.5</v>
       </c>
       <c r="O17" t="n">
-        <v>39</v>
+        <v>37.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>11.9</v>
+        <v>12.7</v>
       </c>
       <c r="W17" t="n">
         <v>27</v>
       </c>
       <c r="X17" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.4</v>
+        <v>11.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>-3.5</v>
+        <v>-5.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>236.13</v>
+        <v>225</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>134.54</v>
+        <v>134.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.74</v>
+        <v>-0.62</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2230,99 +2230,60 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>82.27</v>
+        <v>80.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.28</v>
+        <v>13.86</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46231</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46232</v>
+        <v>46241</v>
       </c>
       <c r="B18" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="C18" t="n">
-        <v>67.59999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D18" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E18" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="F18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>19</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="n">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="X18" t="n">
-        <v>16.6</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA18" t="n">
         <v>9</v>
       </c>
-      <c r="Z18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AB18" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>218.6</v>
+        <v>221.37</v>
       </c>
       <c r="AG18" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2331,10 +2292,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>130.39</v>
+        <v>135.21</v>
       </c>
       <c r="AL18" t="n">
-        <v>-4.15</v>
+        <v>0.59</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2342,100 +2303,61 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>15.79</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46232</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46233</v>
+        <v>46242</v>
       </c>
       <c r="B19" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>68.5</v>
+        <v>145.2</v>
       </c>
       <c r="D19" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>27.7</v>
+        <v>33.5</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>41.4</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>34.9</v>
+        <v>100.3</v>
       </c>
       <c r="O19" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>21.6</v>
+        <v>35.5</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>7.1</v>
       </c>
       <c r="W19" t="n">
-        <v>23.1</v>
+        <v>19.2</v>
       </c>
       <c r="X19" t="n">
-        <v>19.1</v>
+        <v>13.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.6</v>
+        <v>10</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>-5.4</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>224.37</v>
+      </c>
+      <c r="AG19" t="n">
         <v>3</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>218.84</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.25</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2444,10 +2366,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>133.09</v>
+        <v>135.61</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2455,67 +2377,61 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46233</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46234</v>
+        <v>46243</v>
       </c>
       <c r="B20" t="n">
-        <v>137.6</v>
+        <v>146.3</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33.4</v>
       </c>
       <c r="F20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="O20" t="n">
         <v>35.1</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
-        <v>24.4</v>
+        <v>16.4</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>10.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0</v>
+        <v>-6.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.8</v>
+        <v>-3.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>221.78</v>
+        <v>225.93</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2524,10 +2440,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>138.76</v>
+        <v>135.28</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.67</v>
+        <v>-0.33</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2536,60 +2452,93 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46234</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="B21" t="n">
-        <v>132.5</v>
+        <v>182.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>86.8</v>
       </c>
       <c r="D21" t="n">
-        <v>33.6</v>
+        <v>31.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41.1</v>
       </c>
       <c r="K21" t="n">
-        <v>97.8</v>
+        <v>74.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>33.5</v>
       </c>
       <c r="O21" t="n">
-        <v>31.6</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>22.4</v>
       </c>
       <c r="V21" t="n">
-        <v>14.8</v>
+        <v>9.1</v>
       </c>
       <c r="W21" t="n">
-        <v>24.7</v>
+        <v>15</v>
       </c>
       <c r="X21" t="n">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AA21" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.6</v>
+        <v>-10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>-5.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>224.78</v>
+        <v>218.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>-7.3</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2598,10 +2547,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>143.55</v>
+        <v>126.27</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.79</v>
+        <v>-9.01</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2609,94 +2558,100 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46236</v>
+        <v>46245</v>
       </c>
       <c r="B22" t="n">
-        <v>137.2</v>
+        <v>181.8</v>
       </c>
       <c r="C22" t="n">
-        <v>56.3</v>
+        <v>86.5</v>
       </c>
       <c r="D22" t="n">
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
       <c r="E22" t="n">
-        <v>21.2</v>
+        <v>34.2</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="H22" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="I22" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="J22" t="n">
-        <v>40.4</v>
+        <v>41.9</v>
       </c>
       <c r="K22" t="n">
-        <v>75.7</v>
+        <v>76.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>29</v>
+        <v>35.7</v>
       </c>
       <c r="O22" t="n">
-        <v>32.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="T22" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="V22" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>24.3</v>
+        <v>14.8</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
       <c r="Y22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z22" t="n">
         <v>12</v>
       </c>
-      <c r="Z22" t="n">
-        <v>15</v>
-      </c>
       <c r="AA22" t="n">
-        <v>15.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9</v>
+        <v>-4.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>232.22</v>
+        <v>216.39</v>
       </c>
       <c r="AG22" t="n">
-        <v>7.43</v>
+        <v>-2.23</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2660,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>143.61</v>
+        <v>123.32</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.06</v>
+        <v>-2.95</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2717,99 +2672,111 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>89.31999999999999</v>
+        <v>79.08</v>
       </c>
       <c r="AS22" t="n">
-        <v>18.02</v>
+        <v>13.91</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46236</v>
+        <v>46245</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4649.3</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2021.1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>3016.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B23" t="n">
-        <v>157.5</v>
+        <v>183</v>
       </c>
       <c r="C23" t="n">
-        <v>59.6</v>
+        <v>84.7</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>30.9</v>
       </c>
       <c r="E23" t="n">
-        <v>30.6</v>
+        <v>33.7</v>
       </c>
       <c r="F23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="I23" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="J23" t="n">
-        <v>38.9</v>
+        <v>42.3</v>
       </c>
       <c r="K23" t="n">
-        <v>74.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>33.4</v>
+        <v>36.7</v>
       </c>
       <c r="O23" t="n">
-        <v>37.1</v>
+        <v>40.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="T23" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" t="n">
         <v>13</v>
       </c>
-      <c r="W23" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>16</v>
-      </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2.1</v>
+        <v>0.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>229.69</v>
+        <v>217.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>-2.53</v>
+        <v>0.76</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2818,10 +2785,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>136.96</v>
+        <v>117.87</v>
       </c>
       <c r="AL23" t="n">
-        <v>-6.65</v>
+        <v>-5.45</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2830,99 +2797,78 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>86.59</v>
+        <v>78.56</v>
       </c>
       <c r="AS23" t="n">
-        <v>16.96</v>
+        <v>13.45</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6995.8</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2380.8</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>3192.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B24" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="C24" t="n">
-        <v>63</v>
+        <v>163.8</v>
       </c>
       <c r="D24" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>40.5</v>
+        <v>6.5</v>
       </c>
       <c r="K24" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>34.3</v>
+        <v>101.2</v>
       </c>
       <c r="O24" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>21.3</v>
+        <v>40.2</v>
       </c>
       <c r="V24" t="n">
-        <v>17.5</v>
+        <v>6.3</v>
       </c>
       <c r="W24" t="n">
-        <v>22.5</v>
+        <v>17.2</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AB24" t="n">
-        <v>-2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>228.57</v>
+        <v>220.31</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.14</v>
+        <v>3.16</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2931,10 +2877,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>133.01</v>
+        <v>116.52</v>
       </c>
       <c r="AL24" t="n">
-        <v>-3.95</v>
+        <v>-1.35</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2942,100 +2888,73 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>15.95</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>2827.2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>3152.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="B25" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>62.6</v>
+        <v>155.9</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
-      </c>
-      <c r="E25" t="n">
-        <v>32.2</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I25" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>41.1</v>
+        <v>6.5</v>
       </c>
       <c r="K25" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>32.6</v>
+        <v>99.3</v>
       </c>
       <c r="O25" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>20.9</v>
+        <v>38.5</v>
       </c>
       <c r="V25" t="n">
-        <v>16.4</v>
+        <v>8.9</v>
       </c>
       <c r="W25" t="n">
-        <v>22.8</v>
+        <v>15.8</v>
       </c>
       <c r="X25" t="n">
-        <v>19.6</v>
+        <v>12.4</v>
       </c>
       <c r="Y25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" t="n">
         <v>13</v>
       </c>
-      <c r="Z25" t="n">
-        <v>16</v>
-      </c>
       <c r="AA25" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.08</v>
+        <v>221.99</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3044,10 +2963,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>135.24</v>
+        <v>116.37</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.23</v>
+        <v>-0.15</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3055,100 +2974,73 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>15.4</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46239</v>
+        <v>46248</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>3609.5</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1161.2</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>3077.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46240</v>
+        <v>46249</v>
       </c>
       <c r="B26" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C26" t="n">
-        <v>71.09999999999999</v>
+        <v>141.3</v>
       </c>
       <c r="D26" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>42.6</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>77</v>
-      </c>
-      <c r="M26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>31.5</v>
+        <v>97.8</v>
       </c>
       <c r="O26" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>21</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S26" t="n">
-        <v>6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>21</v>
+        <v>39.8</v>
       </c>
       <c r="V26" t="n">
-        <v>12.7</v>
+        <v>9.5</v>
       </c>
       <c r="W26" t="n">
-        <v>27</v>
+        <v>17.7</v>
       </c>
       <c r="X26" t="n">
-        <v>19.9</v>
+        <v>13.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA26" t="n">
         <v>14</v>
       </c>
-      <c r="AA26" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB26" t="n">
-        <v>-5.2</v>
+        <v>0.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.3</v>
+        <v>3.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>225</v>
+        <v>225.14</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.08</v>
+        <v>3.15</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3157,10 +3049,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>134.62</v>
+        <v>120.64</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.62</v>
+        <v>4.27</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3168,61 +3060,73 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
-      <c r="AP26" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL26" s="1" t="n">
-        <v>46240</v>
+        <v>46249</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1884.4</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>2636.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46241</v>
+        <v>46250</v>
       </c>
       <c r="B27" t="n">
-        <v>151.5</v>
+        <v>131.5</v>
       </c>
       <c r="D27" t="n">
-        <v>35.1</v>
+        <v>27.3</v>
       </c>
       <c r="F27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>97</v>
+      </c>
+      <c r="O27" t="n">
+        <v>35.7</v>
       </c>
       <c r="V27" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>19.4</v>
+        <v>13.9</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>11.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AB27" t="n">
-        <v>-4.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>221.37</v>
+        <v>229.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.05</v>
+        <v>4.84</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3231,10 +3135,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>135.21</v>
+        <v>128.14</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.59</v>
+        <v>7.5</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3243,60 +3147,105 @@
         <v>142</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46241</v>
+        <v>46250</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1894.8</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="B28" t="n">
-        <v>145.2</v>
+        <v>153</v>
+      </c>
+      <c r="C28" t="n">
+        <v>71.8</v>
       </c>
       <c r="D28" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N28" t="n">
         <v>33.5</v>
       </c>
-      <c r="F28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>100.3</v>
-      </c>
       <c r="O28" t="n">
-        <v>35.5</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>23.2</v>
       </c>
       <c r="V28" t="n">
-        <v>7.1</v>
+        <v>11.2</v>
       </c>
       <c r="W28" t="n">
-        <v>19.2</v>
+        <v>13</v>
       </c>
       <c r="X28" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>-5.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>224.37</v>
+        <v>229.96</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>-0.02</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3305,10 +3254,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>135.61</v>
+        <v>128.15</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3316,61 +3265,112 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46242</v>
+        <v>46251</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>2723.2</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="B29" t="n">
-        <v>146.3</v>
+        <v>165.8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>77.3</v>
       </c>
       <c r="D29" t="n">
-        <v>33.4</v>
+        <v>29.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>27.7</v>
       </c>
       <c r="F29" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>41.6</v>
       </c>
       <c r="K29" t="n">
-        <v>98.2</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>35.1</v>
       </c>
       <c r="O29" t="n">
-        <v>35.1</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>23.8</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="W29" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="X29" t="n">
-        <v>10.6</v>
+        <v>13.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>-6.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.2</v>
+        <v>9.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>-3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>225.93</v>
+        <v>227.01</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.56</v>
+        <v>-2.95</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3379,10 +3379,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.28</v>
+        <v>128.86</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3390,94 +3390,112 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>14.52</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46243</v>
+        <v>46252</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>6652.6</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1412.3</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>408</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B30" t="n">
-        <v>182.8</v>
+        <v>158.1</v>
       </c>
       <c r="C30" t="n">
-        <v>86.8</v>
+        <v>73.7</v>
       </c>
       <c r="D30" t="n">
-        <v>31.8</v>
+        <v>30.3</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="H30" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="I30" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="K30" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="O30" t="n">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>22.4</v>
+        <v>23.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z30" t="n">
         <v>15</v>
       </c>
-      <c r="T30" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>15</v>
-      </c>
-      <c r="X30" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>12</v>
-      </c>
       <c r="AA30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC30" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB30" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.3</v>
-      </c>
       <c r="AD30" t="n">
-        <v>-5.1</v>
+        <v>6.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>218.63</v>
+        <v>228.35</v>
       </c>
       <c r="AG30" t="n">
-        <v>-7.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3486,10 +3504,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>126.27</v>
+        <v>130.88</v>
       </c>
       <c r="AL30" t="n">
-        <v>-9.01</v>
+        <v>2.02</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3498,99 +3516,111 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>82.66</v>
+        <v>82.37</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.7</v>
+        <v>14.22</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46244</v>
+        <v>46253</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>4993.3</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>958.6</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>2899.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="B31" t="n">
-        <v>181.8</v>
+        <v>154.9</v>
       </c>
       <c r="C31" t="n">
-        <v>86.5</v>
+        <v>70.2</v>
       </c>
       <c r="D31" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E31" t="n">
-        <v>34.2</v>
+        <v>27.7</v>
       </c>
       <c r="F31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
         <v>5.8</v>
       </c>
-      <c r="H31" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="O31" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF31" t="n">
-        <v>216.39</v>
+        <v>231.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>-2.23</v>
+        <v>2.81</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3599,10 +3629,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>123.32</v>
+        <v>132.55</v>
       </c>
       <c r="AL31" t="n">
-        <v>-2.95</v>
+        <v>1.67</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3611,111 +3641,78 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>79.08</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.91</v>
+        <v>13.1</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="BM31" t="n">
-        <v>40.72</v>
+        <v>33.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>4649.3</v>
+        <v>1514.9</v>
       </c>
       <c r="BO31" t="n">
-        <v>2021.1</v>
+        <v>799.7</v>
       </c>
       <c r="BP31" t="n">
-        <v>3016.3</v>
+        <v>2923.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="B32" t="n">
-        <v>183</v>
-      </c>
-      <c r="C32" t="n">
-        <v>84.7</v>
+        <v>152.2</v>
       </c>
       <c r="D32" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E32" t="n">
-        <v>33.7</v>
+        <v>31</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>42.3</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N32" t="n">
-        <v>36.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S32" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>23.6</v>
+        <v>34.4</v>
       </c>
       <c r="V32" t="n">
-        <v>5.7</v>
+        <v>9.5</v>
       </c>
       <c r="W32" t="n">
-        <v>16.1</v>
+        <v>25.5</v>
       </c>
       <c r="X32" t="n">
-        <v>10.9</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.7</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>217.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.76</v>
+        <v>-3.03</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3724,10 +3721,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>117.87</v>
+        <v>128.02</v>
       </c>
       <c r="AL32" t="n">
-        <v>-5.45</v>
+        <v>-4.53</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3735,79 +3732,73 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="BM32" t="n">
-        <v>40.4</v>
+        <v>35.62</v>
       </c>
       <c r="BN32" t="n">
-        <v>6995.8</v>
+        <v>1526.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>2380.8</v>
+        <v>957.4</v>
       </c>
       <c r="BP32" t="n">
-        <v>3192.8</v>
+        <v>2928.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="B33" t="n">
-        <v>163.8</v>
+        <v>143.9</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>30.8</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="K33" t="n">
-        <v>101.2</v>
+        <v>99.2</v>
       </c>
       <c r="O33" t="n">
-        <v>40.2</v>
+        <v>35.2</v>
       </c>
       <c r="V33" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="W33" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="X33" t="n">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="AF33" t="n">
-        <v>220.31</v>
+        <v>229.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.16</v>
+        <v>1.03</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3816,10 +3807,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>116.52</v>
+        <v>127.06</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.35</v>
+        <v>-0.96</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3828,72 +3819,105 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="BM33" t="n">
-        <v>39.65</v>
+        <v>34.56</v>
       </c>
       <c r="BN33" t="n">
-        <v>2827.2</v>
+        <v>170.6</v>
       </c>
       <c r="BO33" t="n">
-        <v>2051.2</v>
+        <v>130.4</v>
       </c>
       <c r="BP33" t="n">
-        <v>3152.1</v>
+        <v>2825.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46248</v>
+        <v>46257</v>
       </c>
       <c r="B34" t="n">
-        <v>155.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>73.7</v>
       </c>
       <c r="D34" t="n">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="E34" t="n">
+        <v>28.2</v>
       </c>
       <c r="F34" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>40.1</v>
       </c>
       <c r="K34" t="n">
-        <v>99.3</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>32.9</v>
       </c>
       <c r="O34" t="n">
-        <v>38.5</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23.5</v>
       </c>
       <c r="V34" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="W34" t="n">
-        <v>15.8</v>
+        <v>20.1</v>
       </c>
       <c r="X34" t="n">
-        <v>12.4</v>
+        <v>14.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z34" t="n">
         <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>5.7</v>
+        <v>9.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>221.99</v>
+        <v>228.55</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.67</v>
+        <v>-0.61</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3902,10 +3926,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>116.37</v>
+        <v>125.61</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.15</v>
+        <v>-1.45</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3913,73 +3937,112 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46248</v>
+        <v>46257</v>
       </c>
       <c r="BM34" t="n">
-        <v>34.79</v>
+        <v>34.78</v>
       </c>
       <c r="BN34" t="n">
-        <v>3609.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="BO34" t="n">
-        <v>1161.2</v>
+        <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>3077.1</v>
+        <v>2769.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46249</v>
+        <v>46258</v>
       </c>
       <c r="B35" t="n">
-        <v>141.3</v>
+        <v>174.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>26.3</v>
+        <v>32.1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>30.8</v>
       </c>
       <c r="F35" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>39.5</v>
       </c>
       <c r="K35" t="n">
-        <v>97.8</v>
+        <v>74</v>
+      </c>
+      <c r="M35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.8</v>
       </c>
       <c r="O35" t="n">
-        <v>39.8</v>
+        <v>42.6</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>23.1</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>12.8</v>
       </c>
       <c r="W35" t="n">
-        <v>17.7</v>
+        <v>22.1</v>
       </c>
       <c r="X35" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="Y35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z35" t="n">
         <v>13</v>
       </c>
-      <c r="Z35" t="n">
-        <v>15</v>
-      </c>
       <c r="AA35" t="n">
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>225.14</v>
+        <v>219.99</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.15</v>
+        <v>-8.56</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3988,10 +4051,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>120.64</v>
+        <v>124.36</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.27</v>
+        <v>-1.25</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3999,73 +4062,112 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
+      <c r="AP35" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>12.96</v>
+      </c>
       <c r="BL35" s="1" t="n">
-        <v>46249</v>
+        <v>46258</v>
       </c>
       <c r="BM35" t="n">
-        <v>31.22</v>
+        <v>36.78</v>
       </c>
       <c r="BN35" t="n">
-        <v>1884.4</v>
+        <v>108.8</v>
       </c>
       <c r="BO35" t="n">
-        <v>785.2</v>
+        <v>204.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>2636.2</v>
+        <v>2982.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="B36" t="n">
-        <v>131.5</v>
+        <v>163.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>27.3</v>
+        <v>32.9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26</v>
       </c>
       <c r="F36" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD36" t="n">
         <v>5.5</v>
       </c>
-      <c r="K36" t="n">
-        <v>97</v>
-      </c>
-      <c r="O36" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V36" t="n">
-        <v>9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X36" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF36" t="n">
-        <v>229.98</v>
+        <v>219.22</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.84</v>
+        <v>-0.77</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4074,10 +4176,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>128.14</v>
+        <v>120.93</v>
       </c>
       <c r="AL36" t="n">
-        <v>7.5</v>
+        <v>-3.43</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4085,106 +4187,112 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>12.38</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="BM36" t="n">
-        <v>26.41</v>
+        <v>32.64</v>
       </c>
       <c r="BN36" t="n">
-        <v>1894.8</v>
+        <v>42.3</v>
       </c>
       <c r="BO36" t="n">
-        <v>223.6</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>3194.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B37" t="n">
-        <v>153</v>
+        <v>152.7</v>
       </c>
       <c r="C37" t="n">
-        <v>71.8</v>
+        <v>62.6</v>
       </c>
       <c r="D37" t="n">
-        <v>28.6</v>
+        <v>32.7</v>
       </c>
       <c r="E37" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="H37" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I37" t="n">
-        <v>10.7</v>
+        <v>7.2</v>
       </c>
       <c r="J37" t="n">
-        <v>41.1</v>
+        <v>38.9</v>
       </c>
       <c r="K37" t="n">
-        <v>75.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="N37" t="n">
         <v>33.5</v>
       </c>
       <c r="O37" t="n">
-        <v>38.3</v>
+        <v>40.1</v>
       </c>
       <c r="Q37" t="n">
         <v>23.2</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
         <v>23.2</v>
       </c>
       <c r="V37" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="W37" t="n">
-        <v>13</v>
+        <v>27.3</v>
       </c>
       <c r="X37" t="n">
-        <v>12.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA37" t="n">
         <v>14</v>
       </c>
-      <c r="AA37" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AB37" t="n">
-        <v>-6.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.6</v>
+        <v>5.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>229.96</v>
+        <v>220.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.02</v>
+        <v>1.5</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4193,10 +4301,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>128.15</v>
+        <v>120.28</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.01</v>
+        <v>-0.65</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4205,111 +4313,111 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>87.47</v>
+        <v>77.87</v>
       </c>
       <c r="AS37" t="n">
-        <v>14.8</v>
+        <v>13.26</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="BM37" t="n">
-        <v>29.83</v>
+        <v>29.61</v>
       </c>
       <c r="BN37" t="n">
-        <v>2723.2</v>
+        <v>60.1</v>
       </c>
       <c r="BO37" t="n">
-        <v>271.1</v>
+        <v>0</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>2717.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="B38" t="n">
-        <v>165.8</v>
+        <v>150.7</v>
       </c>
       <c r="C38" t="n">
-        <v>77.3</v>
+        <v>64.8</v>
       </c>
       <c r="D38" t="n">
-        <v>29.3</v>
+        <v>33.7</v>
       </c>
       <c r="E38" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="F38" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H38" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="I38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>33</v>
+      </c>
+      <c r="O38" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC38" t="n">
         <v>10.8</v>
       </c>
-      <c r="J38" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="K38" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N38" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>7</v>
-      </c>
-      <c r="T38" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X38" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD38" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>227.01</v>
+        <v>220.58</v>
       </c>
       <c r="AG38" t="n">
-        <v>-2.95</v>
+        <v>-0.15</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4318,10 +4426,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.86</v>
+        <v>119.29</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.71</v>
+        <v>-0.99</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4330,111 +4438,72 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>83.41</v>
+        <v>77.22</v>
       </c>
       <c r="AS38" t="n">
-        <v>14.52</v>
+        <v>13.79</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="BM38" t="n">
-        <v>33.62</v>
+        <v>31.11</v>
       </c>
       <c r="BN38" t="n">
-        <v>6652.6</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BO38" t="n">
-        <v>1412.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="BP38" t="n">
-        <v>408</v>
+        <v>3028.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B39" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>73.7</v>
+        <v>138.2</v>
       </c>
       <c r="D39" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E39" t="n">
-        <v>26</v>
+        <v>33.6</v>
       </c>
       <c r="F39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J39" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="K39" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>7</v>
-      </c>
-      <c r="T39" t="n">
-        <v>23.6</v>
+        <v>6.1</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>15.5</v>
       </c>
       <c r="W39" t="n">
-        <v>19.3</v>
+        <v>23.4</v>
       </c>
       <c r="X39" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="AC39" t="n">
         <v>8.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>228.35</v>
+        <v>223.43</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.33</v>
+        <v>2.85</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4443,10 +4512,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>130.88</v>
+        <v>121.35</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4454,112 +4523,67 @@
       <c r="AN39" t="n">
         <v>142</v>
       </c>
-      <c r="AP39" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>14.22</v>
-      </c>
       <c r="BL39" s="1" t="n">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="BM39" t="n">
-        <v>32.38</v>
+        <v>30.59</v>
       </c>
       <c r="BN39" t="n">
-        <v>4993.3</v>
+        <v>40.8</v>
       </c>
       <c r="BO39" t="n">
-        <v>958.6</v>
+        <v>0</v>
       </c>
       <c r="BP39" t="n">
-        <v>2899.8</v>
+        <v>2959.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46254</v>
+        <v>46263</v>
       </c>
       <c r="B40" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C40" t="n">
-        <v>70.2</v>
+        <v>126.5</v>
       </c>
       <c r="D40" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>27.7</v>
+        <v>33.2</v>
       </c>
       <c r="F40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K40" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O40" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T40" t="n">
-        <v>23.7</v>
+        <v>3.4</v>
       </c>
       <c r="V40" t="n">
-        <v>6.3</v>
+        <v>12.6</v>
       </c>
       <c r="W40" t="n">
-        <v>25.2</v>
+        <v>22.3</v>
       </c>
       <c r="X40" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="Y40" t="n">
         <v>8</v>
       </c>
       <c r="Z40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>231.16</v>
+        <v>229.48</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.81</v>
+        <v>6.05</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4568,10 +4592,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>132.55</v>
+        <v>128.37</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.67</v>
+        <v>7.02</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4579,79 +4603,106 @@
       <c r="AN40" t="n">
         <v>142</v>
       </c>
-      <c r="AP40" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL40" s="1" t="n">
-        <v>46254</v>
+        <v>46263</v>
       </c>
       <c r="BM40" t="n">
-        <v>33.01</v>
+        <v>30.05</v>
       </c>
       <c r="BN40" t="n">
-        <v>1514.9</v>
+        <v>34</v>
       </c>
       <c r="BO40" t="n">
-        <v>799.7</v>
+        <v>0</v>
       </c>
       <c r="BP40" t="n">
-        <v>2923.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46255</v>
+        <v>46264</v>
       </c>
       <c r="B41" t="n">
-        <v>152.2</v>
+        <v>129.4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>50.6</v>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>31.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>19.4</v>
       </c>
       <c r="F41" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>38.9</v>
       </c>
       <c r="K41" t="n">
-        <v>98.40000000000001</v>
+        <v>73.3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N41" t="n">
+        <v>33.3</v>
       </c>
       <c r="O41" t="n">
-        <v>34.4</v>
+        <v>38</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>21.4</v>
       </c>
       <c r="V41" t="n">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
       <c r="W41" t="n">
-        <v>25.5</v>
+        <v>23.9</v>
       </c>
       <c r="X41" t="n">
-        <v>17.5</v>
+        <v>19.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>241.48</v>
+      </c>
+      <c r="AG41" t="n">
         <v>12</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>228.13</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>-3.03</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4660,10 +4711,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>128.02</v>
+        <v>134.59</v>
       </c>
       <c r="AL41" t="n">
-        <v>-4.53</v>
+        <v>6.22</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4671,73 +4722,112 @@
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46255</v>
+        <v>46264</v>
       </c>
       <c r="BM41" t="n">
-        <v>35.62</v>
+        <v>24.86</v>
       </c>
       <c r="BN41" t="n">
-        <v>1526.5</v>
+        <v>80.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>957.4</v>
+        <v>0</v>
       </c>
       <c r="BP41" t="n">
-        <v>2928.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="B42" t="n">
-        <v>143.9</v>
+        <v>142.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>52.7</v>
       </c>
       <c r="D42" t="n">
-        <v>30.8</v>
+        <v>34.7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>24.8</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>22</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>38.2</v>
       </c>
       <c r="K42" t="n">
-        <v>99.2</v>
+        <v>70</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>31.9</v>
       </c>
       <c r="O42" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>19.7</v>
       </c>
       <c r="V42" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="W42" t="n">
-        <v>17.6</v>
+        <v>25.8</v>
       </c>
       <c r="X42" t="n">
-        <v>14.2</v>
+        <v>18.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF42" t="n">
-        <v>229.16</v>
+        <v>238.69</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.03</v>
+        <v>-2.8</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4746,10 +4836,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>127.06</v>
+        <v>136.6</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.96</v>
+        <v>2.01</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4757,106 +4847,112 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>17.06</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="BM42" t="n">
-        <v>34.56</v>
+        <v>29.8</v>
       </c>
       <c r="BN42" t="n">
-        <v>170.6</v>
+        <v>61.9</v>
       </c>
       <c r="BO42" t="n">
-        <v>130.4</v>
+        <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>2825.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46257</v>
+        <v>46266</v>
       </c>
       <c r="B43" t="n">
-        <v>163.2</v>
+        <v>148.1</v>
       </c>
       <c r="C43" t="n">
-        <v>73.7</v>
+        <v>51.9</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>35.4</v>
       </c>
       <c r="E43" t="n">
-        <v>28.2</v>
+        <v>31.5</v>
       </c>
       <c r="F43" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>24.1</v>
+        <v>21.8</v>
       </c>
       <c r="I43" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="J43" t="n">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="K43" t="n">
-        <v>75.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="M43" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="N43" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="O43" t="n">
-        <v>39.7</v>
+        <v>33.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>23.5</v>
+        <v>20.7</v>
       </c>
       <c r="R43" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>23.5</v>
+        <v>20.7</v>
       </c>
       <c r="V43" t="n">
-        <v>9.4</v>
+        <v>13.1</v>
       </c>
       <c r="W43" t="n">
-        <v>20.1</v>
+        <v>25.5</v>
       </c>
       <c r="X43" t="n">
-        <v>14.8</v>
+        <v>19.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>9.300000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AF43" t="n">
-        <v>228.55</v>
+        <v>233.48</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.61</v>
+        <v>-4.86</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4865,10 +4961,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>125.61</v>
+        <v>135.66</v>
       </c>
       <c r="AL43" t="n">
-        <v>-1.45</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4877,111 +4973,111 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>82.81</v>
+        <v>86.25</v>
       </c>
       <c r="AS43" t="n">
-        <v>12.9</v>
+        <v>17.13</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46257</v>
+        <v>46266</v>
       </c>
       <c r="BM43" t="n">
-        <v>34.78</v>
+        <v>36.03</v>
       </c>
       <c r="BN43" t="n">
-        <v>69.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="BO43" t="n">
         <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>2769.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="B44" t="n">
-        <v>174.4</v>
+        <v>143.4</v>
       </c>
       <c r="C44" t="n">
-        <v>75.40000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="D44" t="n">
-        <v>32.1</v>
+        <v>35.7</v>
       </c>
       <c r="E44" t="n">
-        <v>30.8</v>
+        <v>26.2</v>
       </c>
       <c r="F44" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="I44" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="K44" t="n">
-        <v>74</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>35.8</v>
+        <v>31.2</v>
       </c>
       <c r="O44" t="n">
-        <v>42.6</v>
+        <v>33.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.1</v>
+        <v>21.6</v>
       </c>
       <c r="R44" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>23.1</v>
+        <v>21.6</v>
       </c>
       <c r="V44" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W44" t="n">
-        <v>22.1</v>
+        <v>28.3</v>
       </c>
       <c r="X44" t="n">
-        <v>17.5</v>
+        <v>20.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA44" t="n">
-        <v>10.1</v>
+        <v>17.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AF44" t="n">
-        <v>219.99</v>
+        <v>235.13</v>
       </c>
       <c r="AG44" t="n">
-        <v>-8.56</v>
+        <v>1.66</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4990,10 +5086,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>124.36</v>
+        <v>136.33</v>
       </c>
       <c r="AL44" t="n">
-        <v>-1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -5002,111 +5098,111 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>77.83</v>
+        <v>88.27</v>
       </c>
       <c r="AS44" t="n">
-        <v>12.96</v>
+        <v>17.6</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="BM44" t="n">
-        <v>36.78</v>
+        <v>32</v>
       </c>
       <c r="BN44" t="n">
-        <v>108.8</v>
+        <v>29.5</v>
       </c>
       <c r="BO44" t="n">
-        <v>204.3</v>
+        <v>0</v>
       </c>
       <c r="BP44" t="n">
-        <v>2982.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="B45" t="n">
-        <v>163.2</v>
+        <v>144.9</v>
       </c>
       <c r="C45" t="n">
-        <v>70.90000000000001</v>
+        <v>53</v>
       </c>
       <c r="D45" t="n">
-        <v>32.9</v>
+        <v>35.6</v>
       </c>
       <c r="E45" t="n">
         <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="H45" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="J45" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="K45" t="n">
-        <v>71.3</v>
+        <v>73.7</v>
       </c>
       <c r="M45" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="N45" t="n">
-        <v>34.3</v>
+        <v>31.6</v>
       </c>
       <c r="O45" t="n">
-        <v>41.5</v>
+        <v>33.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.1</v>
+        <v>21</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>23.1</v>
+        <v>21</v>
       </c>
       <c r="V45" t="n">
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="W45" t="n">
-        <v>23.3</v>
+        <v>27.7</v>
       </c>
       <c r="X45" t="n">
-        <v>16.4</v>
+        <v>21.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z45" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="n">
-        <v>12.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.6</v>
+        <v>-1.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>219.22</v>
+        <v>234.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.77</v>
+        <v>-0.26</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5115,10 +5211,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>120.93</v>
+        <v>137.17</v>
       </c>
       <c r="AL45" t="n">
-        <v>-3.43</v>
+        <v>0.84</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5127,111 +5223,72 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>76.81</v>
+        <v>87.09</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.38</v>
+        <v>17.31</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="BM45" t="n">
-        <v>32.64</v>
+        <v>32.57</v>
       </c>
       <c r="BN45" t="n">
-        <v>42.3</v>
+        <v>23.4</v>
       </c>
       <c r="BO45" t="n">
-        <v>95.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP45" t="n">
-        <v>3194.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="B46" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="C46" t="n">
-        <v>62.6</v>
+        <v>132.2</v>
       </c>
       <c r="D46" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E46" t="n">
-        <v>24.6</v>
+        <v>35.6</v>
       </c>
       <c r="F46" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K46" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N46" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O46" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="V46" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W46" t="n">
         <v>23.2</v>
       </c>
-      <c r="R46" t="n">
+      <c r="X46" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD46" t="n">
         <v>4.2</v>
       </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V46" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W46" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF46" t="n">
-        <v>220.73</v>
+        <v>234.78</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.5</v>
+        <v>-0.09</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5240,10 +5297,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>120.28</v>
+        <v>136.08</v>
       </c>
       <c r="AL46" t="n">
-        <v>-0.65</v>
+        <v>-1.09</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5251,112 +5308,67 @@
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>77.87</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>13.26</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="BM46" t="n">
-        <v>29.61</v>
+        <v>29.64</v>
       </c>
       <c r="BN46" t="n">
-        <v>60.1</v>
+        <v>36.4</v>
       </c>
       <c r="BO46" t="n">
         <v>0</v>
       </c>
       <c r="BP46" t="n">
-        <v>2717.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46261</v>
+        <v>46270</v>
       </c>
       <c r="B47" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C47" t="n">
-        <v>64.8</v>
+        <v>137.1</v>
       </c>
       <c r="D47" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E47" t="n">
-        <v>27.1</v>
+        <v>35.1</v>
       </c>
       <c r="F47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K47" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N47" t="n">
-        <v>33</v>
-      </c>
-      <c r="O47" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>23.2</v>
+        <v>3.3</v>
       </c>
       <c r="V47" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="W47" t="n">
-        <v>28.9</v>
+        <v>22</v>
       </c>
       <c r="X47" t="n">
-        <v>21.7</v>
+        <v>16.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA47" t="n">
-        <v>13.1</v>
+        <v>10.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AC47" t="n">
-        <v>10.8</v>
+        <v>6.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="AF47" t="n">
-        <v>220.58</v>
+        <v>229.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.15</v>
+        <v>-5.03</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5365,10 +5377,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>119.29</v>
+        <v>135.42</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5376,73 +5388,88 @@
       <c r="AN47" t="n">
         <v>142</v>
       </c>
-      <c r="AP47" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL47" s="1" t="n">
-        <v>46261</v>
+        <v>46270</v>
       </c>
       <c r="BM47" t="n">
-        <v>31.11</v>
+        <v>31.45</v>
       </c>
       <c r="BN47" t="n">
-        <v>87.90000000000001</v>
+        <v>35.9</v>
       </c>
       <c r="BO47" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP47" t="n">
-        <v>3028.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46262</v>
+        <v>46271</v>
       </c>
       <c r="B48" t="n">
-        <v>138.2</v>
+        <v>166.2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>28.1</v>
       </c>
       <c r="F48" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V48" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H48" t="n">
         <v>23.4</v>
       </c>
-      <c r="X48" t="n">
-        <v>19.4</v>
+      <c r="I48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J48" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AA48" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF48" t="n">
-        <v>223.43</v>
+        <v>222.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.85</v>
+        <v>-6.9</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5451,10 +5478,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>121.35</v>
+        <v>131.24</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.06</v>
+        <v>-4.18</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5462,67 +5489,94 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46262</v>
+        <v>46271</v>
       </c>
       <c r="BM48" t="n">
-        <v>30.59</v>
+        <v>34.46</v>
       </c>
       <c r="BN48" t="n">
-        <v>40.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>373.6</v>
       </c>
       <c r="BP48" t="n">
-        <v>2959.2</v>
+        <v>249.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46263</v>
+        <v>46272</v>
       </c>
       <c r="B49" t="n">
-        <v>126.5</v>
+        <v>166.3</v>
+      </c>
+      <c r="C49" t="n">
+        <v>74.90000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>28.8</v>
       </c>
       <c r="F49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V49" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X49" t="n">
-        <v>17.4</v>
+        <v>4.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J49" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="AF49" t="n">
-        <v>229.48</v>
+        <v>218.37</v>
       </c>
       <c r="AG49" t="n">
-        <v>6.05</v>
+        <v>-4.49</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5531,10 +5585,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>128.37</v>
+        <v>129.21</v>
       </c>
       <c r="AL49" t="n">
-        <v>7.02</v>
+        <v>-2.03</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5542,106 +5596,94 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
+      <c r="AP49" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>12.97</v>
+      </c>
       <c r="BL49" s="1" t="n">
-        <v>46263</v>
+        <v>46272</v>
       </c>
       <c r="BM49" t="n">
-        <v>30.05</v>
+        <v>35.4</v>
       </c>
       <c r="BN49" t="n">
-        <v>34</v>
+        <v>294.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="BP49" t="n">
-        <v>0</v>
+        <v>2758.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46264</v>
+        <v>46273</v>
       </c>
       <c r="B50" t="n">
-        <v>129.4</v>
+        <v>154.1</v>
       </c>
       <c r="C50" t="n">
-        <v>50.6</v>
+        <v>65</v>
       </c>
       <c r="D50" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="E50" t="n">
-        <v>19.4</v>
+        <v>25.2</v>
       </c>
       <c r="F50" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="I50" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="K50" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="N50" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="O50" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T50" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="V50" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="W50" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X50" t="n">
-        <v>19.1</v>
+        <v>21.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>241.48</v>
+        <v>220.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>12</v>
+        <v>2.48</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5650,10 +5692,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>134.59</v>
+        <v>129.07</v>
       </c>
       <c r="AL50" t="n">
-        <v>6.22</v>
+        <v>-0.14</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5662,111 +5704,93 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>91.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46264</v>
+        <v>46273</v>
       </c>
       <c r="BM50" t="n">
-        <v>24.86</v>
+        <v>32.31</v>
       </c>
       <c r="BN50" t="n">
-        <v>80.2</v>
+        <v>547</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BP50" t="n">
-        <v>0</v>
+        <v>2654.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="B51" t="n">
-        <v>142.9</v>
+        <v>148.8</v>
       </c>
       <c r="C51" t="n">
-        <v>52.7</v>
+        <v>57.6</v>
       </c>
       <c r="D51" t="n">
-        <v>34.7</v>
+        <v>32.7</v>
       </c>
       <c r="E51" t="n">
-        <v>24.8</v>
+        <v>26.3</v>
       </c>
       <c r="F51" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H51" t="n">
-        <v>22</v>
+        <v>23.6</v>
       </c>
       <c r="I51" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="J51" t="n">
-        <v>38.2</v>
+        <v>41.6</v>
       </c>
       <c r="K51" t="n">
-        <v>70</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="N51" t="n">
-        <v>31.9</v>
+        <v>35</v>
       </c>
       <c r="O51" t="n">
-        <v>35.8</v>
+        <v>42.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V51" t="n">
-        <v>12</v>
-      </c>
-      <c r="W51" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X51" t="n">
-        <v>18.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
         <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2.9</v>
+        <v>15.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>238.69</v>
+        <v>220.84</v>
       </c>
       <c r="AG51" t="n">
-        <v>-2.8</v>
+        <v>-0.01</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5775,10 +5799,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>136.6</v>
+        <v>130.73</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5787,111 +5811,93 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>89.05</v>
+        <v>85.52</v>
       </c>
       <c r="AS51" t="n">
-        <v>17.06</v>
+        <v>15.82</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="BM51" t="n">
-        <v>29.8</v>
+        <v>31.51</v>
       </c>
       <c r="BN51" t="n">
-        <v>61.9</v>
+        <v>124</v>
       </c>
       <c r="BO51" t="n">
-        <v>0</v>
+        <v>164.4</v>
       </c>
       <c r="BP51" t="n">
-        <v>0</v>
+        <v>2635.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="B52" t="n">
-        <v>148.1</v>
+        <v>146.8</v>
       </c>
       <c r="C52" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
       <c r="D52" t="n">
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="E52" t="n">
-        <v>31.5</v>
+        <v>28.9</v>
       </c>
       <c r="F52" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="H52" t="n">
-        <v>21.8</v>
+        <v>23.7</v>
       </c>
       <c r="I52" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="J52" t="n">
-        <v>39.6</v>
+        <v>40.8</v>
       </c>
       <c r="K52" t="n">
-        <v>71</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="N52" t="n">
-        <v>30.8</v>
+        <v>33.1</v>
       </c>
       <c r="O52" t="n">
-        <v>33.7</v>
+        <v>38.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="R52" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="V52" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X52" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z52" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.7</v>
+        <v>16.1</v>
       </c>
       <c r="AF52" t="n">
-        <v>233.48</v>
+        <v>225.87</v>
       </c>
       <c r="AG52" t="n">
-        <v>-4.86</v>
+        <v>5.03</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5900,10 +5906,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>135.66</v>
+        <v>132</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5912,111 +5918,48 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>86.25</v>
+        <v>88.2</v>
       </c>
       <c r="AS52" t="n">
-        <v>17.13</v>
+        <v>15.76</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="BM52" t="n">
-        <v>36.03</v>
+        <v>34.36</v>
       </c>
       <c r="BN52" t="n">
-        <v>76.5</v>
+        <v>62.8</v>
       </c>
       <c r="BO52" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>2693.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46267</v>
+        <v>46276</v>
       </c>
       <c r="B53" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="C53" t="n">
-        <v>50.9</v>
+        <v>133.9</v>
       </c>
       <c r="D53" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E53" t="n">
-        <v>26.2</v>
+        <v>34.7</v>
       </c>
       <c r="F53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H53" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I53" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J53" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K53" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2</v>
-      </c>
-      <c r="N53" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V53" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W53" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="X53" t="n">
-        <v>20.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA53" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>235.13</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.66</v>
+        <v>15</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -6024,124 +5967,37 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
-      <c r="AK53" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
-      <c r="AP53" t="n">
-        <v>88.27</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>17.6</v>
-      </c>
       <c r="BL53" s="1" t="n">
-        <v>46267</v>
-      </c>
-      <c r="BM53" t="n">
-        <v>32</v>
-      </c>
-      <c r="BN53" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="BO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP53" t="n">
-        <v>0</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B54" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C54" t="n">
-        <v>53</v>
+        <v>137.5</v>
       </c>
       <c r="D54" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>26</v>
+        <v>32.8</v>
       </c>
       <c r="F54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H54" t="n">
-        <v>24</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K54" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N54" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O54" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>21</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>21</v>
-      </c>
-      <c r="V54" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W54" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X54" t="n">
-        <v>21.1</v>
+        <v>2.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA54" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>234.87</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>-0.26</v>
+        <v>10.5</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -6149,85 +6005,19 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
-      <c r="AK54" t="n">
-        <v>137.17</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.84</v>
-      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
-      <c r="AP54" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL54" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="BM54" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="BN54" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="BO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP54" t="n">
-        <v>0</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B55" t="n">
-        <v>132.2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W55" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>234.78</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>-0.09</v>
+        <v>46278</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6235,12 +6025,6 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>136.08</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>-1.09</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
@@ -6248,66 +6032,12 @@
         <v>142</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="BM55" t="n">
-        <v>29.64</v>
-      </c>
-      <c r="BN55" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>0</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B56" t="n">
-        <v>137.1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>11</v>
-      </c>
-      <c r="W56" t="n">
-        <v>22</v>
-      </c>
-      <c r="X56" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>229.75</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>-5.03</v>
+        <v>46279</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -6315,12 +6045,6 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
-      <c r="AK56" t="n">
-        <v>135.42</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>-0.66</v>
-      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
@@ -6328,87 +6052,12 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="BM56" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="BN56" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="BO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP56" t="n">
-        <v>0</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B57" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="C57" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D57" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E57" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M57" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N57" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="O57" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>222.86</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>-6.9</v>
+        <v>46280</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6416,106 +6065,19 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>-4.18</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>81.98</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>15.01</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>34.46</v>
-      </c>
-      <c r="BN57" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="BO57" t="n">
-        <v>373.6</v>
-      </c>
-      <c r="BP57" t="n">
-        <v>249.4</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B58" t="n">
-        <v>166.3</v>
-      </c>
-      <c r="C58" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="D58" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E58" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J58" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="K58" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="O58" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>218.37</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-4.49</v>
+        <v>46281</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6523,106 +6085,19 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>129.21</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-2.03</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>12.97</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="BN58" t="n">
-        <v>294.2</v>
-      </c>
-      <c r="BO58" t="n">
-        <v>227</v>
-      </c>
-      <c r="BP58" t="n">
-        <v>2758.6</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B59" t="n">
-        <v>154.1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>65</v>
-      </c>
-      <c r="D59" t="n">
-        <v>32</v>
-      </c>
-      <c r="E59" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="F59" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H59" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9</v>
-      </c>
-      <c r="J59" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="M59" t="n">
-        <v>8</v>
-      </c>
-      <c r="N59" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="O59" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R59" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T59" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>220.85</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>2.48</v>
+        <v>46282</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6630,106 +6105,19 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>129.07</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>-0.14</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>15.23</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="BM59" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="BN59" t="n">
-        <v>547</v>
-      </c>
-      <c r="BO59" t="n">
-        <v>85</v>
-      </c>
-      <c r="BP59" t="n">
-        <v>2654.5</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B60" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="C60" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E60" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="F60" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J60" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="K60" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="M60" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N60" t="n">
-        <v>35</v>
-      </c>
-      <c r="O60" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R60" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>220.84</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>-0.01</v>
+        <v>46283</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6737,76 +6125,19 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
-      <c r="AK60" t="n">
-        <v>130.73</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
-      <c r="AP60" t="n">
-        <v>85.52</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>15.82</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="BM60" t="n">
-        <v>31.51</v>
-      </c>
-      <c r="BN60" t="n">
-        <v>124</v>
-      </c>
-      <c r="BO60" t="n">
-        <v>164.4</v>
-      </c>
-      <c r="BP60" t="n">
-        <v>2635.8</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B61" t="n">
-        <v>131.7</v>
-      </c>
-      <c r="D61" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H61" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I61" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J61" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="M61" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N61" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>15.5</v>
+        <v>46284</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6814,12 +6145,6 @@
       <c r="AI61" t="n">
         <v>235</v>
       </c>
-      <c r="AK61" t="n">
-        <v>132</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AM61" t="n">
         <v>110</v>
       </c>
@@ -6827,42 +6152,12 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>2693.4</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B62" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="D62" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="F62" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>15</v>
+        <v>46285</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6877,7 +6172,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46276</v>
+        <v>46285</v>
       </c>
     </row>
   </sheetData>
